--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C9D376-FFC4-48C5-A18A-B32FFF4BB5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47AEC718-7C85-4EE6-9B6C-B83077CC3646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="426">
   <si>
     <t>Darmanethan</t>
   </si>
@@ -1312,6 +1312,9 @@
   </si>
   <si>
     <t>992 958 823</t>
+  </si>
+  <si>
+    <t>1 33 4442 1918</t>
   </si>
 </sst>
 </file>
@@ -2909,6 +2912,9 @@
       <c r="A72" t="s">
         <v>194</v>
       </c>
+      <c r="B72" t="s">
+        <v>425</v>
+      </c>
       <c r="C72" t="s">
         <v>267</v>
       </c>
@@ -2917,7 +2923,7 @@
       </c>
       <c r="E72" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+52 </v>
+        <v>+52 1 33 4442 1918</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">

--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47AEC718-7C85-4EE6-9B6C-B83077CC3646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE8A97D-064D-48FC-9391-BFB81D2F1E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="427">
   <si>
     <t>Darmanethan</t>
   </si>
@@ -1315,6 +1315,9 @@
   </si>
   <si>
     <t>1 33 4442 1918</t>
+  </si>
+  <si>
+    <t>991 846 357</t>
   </si>
 </sst>
 </file>
@@ -1701,6 +1704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:F273"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1726,7 +1730,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -1741,7 +1745,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>236</v>
       </c>
@@ -1759,7 +1763,7 @@
         <v>+51 933 668 277</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>41</v>
       </c>
@@ -1777,7 +1781,7 @@
         <v>+51 980 596 555</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -1795,7 +1799,7 @@
         <v>+58 424-7086947</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>83</v>
       </c>
@@ -1810,7 +1814,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>235</v>
       </c>
@@ -1828,7 +1832,7 @@
         <v>+58 412-1322018</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>193</v>
       </c>
@@ -1846,7 +1850,7 @@
         <v>+56 9 7927 3083</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>113</v>
       </c>
@@ -1861,7 +1865,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1879,7 +1883,7 @@
         <v>+51 985 699 608</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -1897,7 +1901,7 @@
         <v>+52 1 56 1007 9583</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>191</v>
       </c>
@@ -1915,7 +1919,7 @@
         <v>+52 1 81 2944 2313</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>84</v>
       </c>
@@ -1930,7 +1934,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>92</v>
       </c>
@@ -1945,7 +1949,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>160</v>
       </c>
@@ -1960,7 +1964,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -1978,7 +1982,7 @@
         <v>+51  984 190 584</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>149</v>
       </c>
@@ -1993,7 +1997,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -2011,7 +2015,7 @@
         <v>+51 984 267 160</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -2029,7 +2033,7 @@
         <v>+51  912 858 811</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>127</v>
       </c>
@@ -2044,7 +2048,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>136</v>
       </c>
@@ -2062,7 +2066,7 @@
         <v>+51 949 647 819</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -2080,7 +2084,7 @@
         <v>+34  646 20 50 99</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>228</v>
       </c>
@@ -2095,7 +2099,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>137</v>
       </c>
@@ -2113,7 +2117,7 @@
         <v>+52  1 222 102 8165</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -2131,7 +2135,7 @@
         <v>+58 416-4398466</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>129</v>
       </c>
@@ -2149,7 +2153,7 @@
         <v>+54 91139028131</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -2167,7 +2171,7 @@
         <v>+57 322 4761144</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -2185,7 +2189,7 @@
         <v>+52 1 771 306 4084</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>234</v>
       </c>
@@ -2203,7 +2207,7 @@
         <v>+58 412-7060529</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -2221,7 +2225,7 @@
         <v>+51 933448842</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>37</v>
       </c>
@@ -2236,7 +2240,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -2254,7 +2258,7 @@
         <v>+51 912358537</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>179</v>
       </c>
@@ -2272,7 +2276,7 @@
         <v>+51 950 746 501</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>54</v>
       </c>
@@ -2290,7 +2294,7 @@
         <v>+54 9 3794 73 7373</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>119</v>
       </c>
@@ -2305,7 +2309,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>180</v>
       </c>
@@ -2323,7 +2327,7 @@
         <v>+55 71 9370-7438</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>254</v>
       </c>
@@ -2341,7 +2345,7 @@
         <v>+51 991 176 689</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>121</v>
       </c>
@@ -2359,7 +2363,7 @@
         <v>+34 601 36 84 69</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>71</v>
       </c>
@@ -2374,7 +2378,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>184</v>
       </c>
@@ -2392,7 +2396,7 @@
         <v>+51  917 057 695</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>51</v>
       </c>
@@ -2410,7 +2414,7 @@
         <v>+34 608 39 51 22</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>221</v>
       </c>
@@ -2425,7 +2429,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>117</v>
       </c>
@@ -2440,7 +2444,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>99</v>
       </c>
@@ -2455,7 +2459,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>198</v>
       </c>
@@ -2473,7 +2477,7 @@
         <v>+54 93854880470</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>61</v>
       </c>
@@ -2491,7 +2495,7 @@
         <v>+53 51162846</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>169</v>
       </c>
@@ -2506,7 +2510,7 @@
         <v xml:space="preserve">+1 </v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>57</v>
       </c>
@@ -2521,7 +2525,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>10</v>
       </c>
@@ -2539,7 +2543,7 @@
         <v>+51  920 449 371</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>68</v>
       </c>
@@ -2557,7 +2561,7 @@
         <v>+51  912 209 142</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>105</v>
       </c>
@@ -2572,7 +2576,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>0</v>
       </c>
@@ -2590,7 +2594,7 @@
         <v>+505 8799 9543</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>125</v>
       </c>
@@ -2608,7 +2612,7 @@
         <v>+52 1 686 589 5829</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>161</v>
       </c>
@@ -2626,7 +2630,7 @@
         <v>+51 992 067 030</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>108</v>
       </c>
@@ -2641,7 +2645,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -2656,7 +2660,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>230</v>
       </c>
@@ -2671,7 +2675,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>32</v>
       </c>
@@ -2689,7 +2693,7 @@
         <v>+58  412-7396859</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>111</v>
       </c>
@@ -2707,7 +2711,7 @@
         <v>+52 1 921 208 0809</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>100</v>
       </c>
@@ -2722,7 +2726,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>166</v>
       </c>
@@ -2740,7 +2744,7 @@
         <v>+504 3204-1711</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>128</v>
       </c>
@@ -2758,7 +2762,7 @@
         <v>+56 99797773</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>222</v>
       </c>
@@ -2773,7 +2777,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>39</v>
       </c>
@@ -2791,7 +2795,7 @@
         <v>+1 305 8902347</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>408</v>
       </c>
@@ -2809,7 +2813,7 @@
         <v>+52 1 861 128 3193</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>124</v>
       </c>
@@ -2824,7 +2828,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>176</v>
       </c>
@@ -2839,7 +2843,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>216</v>
       </c>
@@ -2857,7 +2861,7 @@
         <v>+52 8341048014</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>5</v>
       </c>
@@ -2875,7 +2879,7 @@
         <v>+506  8936 2350</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>159</v>
       </c>
@@ -2893,10 +2897,13 @@
         <v>+1 253 212-8032</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>74</v>
       </c>
+      <c r="B71" s="3" t="s">
+        <v>426</v>
+      </c>
       <c r="C71" t="s">
         <v>270</v>
       </c>
@@ -2905,10 +2912,10 @@
       </c>
       <c r="E71" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+51 </v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+        <v>+51 991 846 357</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>194</v>
       </c>
@@ -2926,7 +2933,7 @@
         <v>+52 1 33 4442 1918</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>110</v>
       </c>
@@ -2941,7 +2948,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>187</v>
       </c>
@@ -2956,7 +2963,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>240</v>
       </c>
@@ -2971,7 +2978,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>31</v>
       </c>
@@ -2989,7 +2996,7 @@
         <v>+51  912 058 374</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>88</v>
       </c>
@@ -3004,7 +3011,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>133</v>
       </c>
@@ -3019,7 +3026,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>90</v>
       </c>
@@ -3034,7 +3041,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>106</v>
       </c>
@@ -3049,7 +3056,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>214</v>
       </c>
@@ -3067,7 +3074,7 @@
         <v>+593  96 083 0485</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>112</v>
       </c>
@@ -3082,7 +3089,7 @@
         <v xml:space="preserve">+505 </v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>107</v>
       </c>
@@ -3097,7 +3104,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>44</v>
       </c>
@@ -3115,7 +3122,7 @@
         <v>+51  983 379 394</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>66</v>
       </c>
@@ -3130,7 +3137,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>162</v>
       </c>
@@ -3148,7 +3155,7 @@
         <v>+51 980 679 898</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>229</v>
       </c>
@@ -3163,7 +3170,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>139</v>
       </c>
@@ -3181,7 +3188,7 @@
         <v>+53  5 6467775</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>175</v>
       </c>
@@ -3199,7 +3206,7 @@
         <v>+51 943126988</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>122</v>
       </c>
@@ -3214,7 +3221,7 @@
         <v xml:space="preserve">+593 </v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>213</v>
       </c>
@@ -3229,7 +3236,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>45</v>
       </c>
@@ -3247,7 +3254,7 @@
         <v>+54 9 3412 81-3587</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>89</v>
       </c>
@@ -3262,7 +3269,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>120</v>
       </c>
@@ -3280,7 +3287,7 @@
         <v>+57  302 5578252</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>205</v>
       </c>
@@ -3298,7 +3305,7 @@
         <v>+593 96 151 5565</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>243</v>
       </c>
@@ -3316,7 +3323,7 @@
         <v>+51 956 677 392</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>239</v>
       </c>
@@ -3334,7 +3341,7 @@
         <v>+54 9 11 2783 9968</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>155</v>
       </c>
@@ -3352,7 +3359,7 @@
         <v>+51 961 492 733</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>34</v>
       </c>
@@ -3370,7 +3377,7 @@
         <v>+53 5 1113536</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>140</v>
       </c>
@@ -3385,7 +3392,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>232</v>
       </c>
@@ -3400,7 +3407,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>141</v>
       </c>
@@ -3415,7 +3422,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>55</v>
       </c>
@@ -3433,7 +3440,7 @@
         <v>+1 809 658-5500</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>154</v>
       </c>
@@ -3451,7 +3458,7 @@
         <v>+58 424-1216695</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>168</v>
       </c>
@@ -3469,7 +3476,7 @@
         <v>+51 963 745 855</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>224</v>
       </c>
@@ -3487,7 +3494,7 @@
         <v>+51  960 274 071</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>114</v>
       </c>
@@ -3505,7 +3512,7 @@
         <v>+593 98 768 2900</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>94</v>
       </c>
@@ -3520,7 +3527,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>246</v>
       </c>
@@ -3538,7 +3545,7 @@
         <v>+503 7868 0662</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>242</v>
       </c>
@@ -3553,7 +3560,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>156</v>
       </c>
@@ -3571,7 +3578,7 @@
         <v>+58 414-4473628</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>43</v>
       </c>
@@ -3589,7 +3596,7 @@
         <v>+57 3054850698</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>223</v>
       </c>
@@ -3604,7 +3611,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>163</v>
       </c>
@@ -3619,7 +3626,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>56</v>
       </c>
@@ -3634,7 +3641,7 @@
         <v xml:space="preserve">+507 </v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>150</v>
       </c>
@@ -3652,7 +3659,7 @@
         <v>+58  412-1885430</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>130</v>
       </c>
@@ -3670,7 +3677,7 @@
         <v>+51  906 691 465</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>146</v>
       </c>
@@ -3685,7 +3692,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>165</v>
       </c>
@@ -3703,7 +3710,7 @@
         <v>+1  787 513-4231</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>46</v>
       </c>
@@ -3721,7 +3728,7 @@
         <v>+507  6898-7574</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>209</v>
       </c>
@@ -3739,7 +3746,7 @@
         <v>+52 1 444 674 9780</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>2</v>
       </c>
@@ -3754,7 +3761,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>21</v>
       </c>
@@ -3772,7 +3779,7 @@
         <v>+51 996 668 615</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>77</v>
       </c>
@@ -3787,7 +3794,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>249</v>
       </c>
@@ -3805,7 +3812,7 @@
         <v>+52 1 55 3845 6274</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>192</v>
       </c>
@@ -3820,7 +3827,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>253</v>
       </c>
@@ -3838,7 +3845,7 @@
         <v>+51  921 447 908</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>12</v>
       </c>
@@ -3856,7 +3863,7 @@
         <v>+51 976 413 331</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>183</v>
       </c>
@@ -3871,7 +3878,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>101</v>
       </c>
@@ -3886,7 +3893,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>157</v>
       </c>
@@ -3901,7 +3908,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>47</v>
       </c>
@@ -3916,7 +3923,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>220</v>
       </c>
@@ -3934,7 +3941,7 @@
         <v>+52 Juni Frostheart</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>257</v>
       </c>
@@ -3952,7 +3959,7 @@
         <v>+54 9 11 2526 8333</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>247</v>
       </c>
@@ -3970,7 +3977,7 @@
         <v>+51 963 347 387</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>33</v>
       </c>
@@ -3988,7 +3995,7 @@
         <v>+52 1 81 2684 3183</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>135</v>
       </c>
@@ -4003,7 +4010,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>178</v>
       </c>
@@ -4018,7 +4025,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>109</v>
       </c>
@@ -4033,7 +4040,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>142</v>
       </c>
@@ -4048,7 +4055,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>26</v>
       </c>
@@ -4066,7 +4073,7 @@
         <v>+57 302 3773516</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -4084,7 +4091,7 @@
         <v>+54  9 11 2372-2211</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>211</v>
       </c>
@@ -4102,7 +4109,7 @@
         <v>+51 960 749 072</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>25</v>
       </c>
@@ -4120,7 +4127,7 @@
         <v>+51 984 784 816</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>244</v>
       </c>
@@ -4138,7 +4145,7 @@
         <v>+51 986 579 683</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>207</v>
       </c>
@@ -4156,7 +4163,7 @@
         <v>+52 1 614 529 6392</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>210</v>
       </c>
@@ -4174,7 +4181,7 @@
         <v>+52 1 287 154 7879</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>174</v>
       </c>
@@ -4189,7 +4196,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>185</v>
       </c>
@@ -4204,7 +4211,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>65</v>
       </c>
@@ -4222,7 +4229,7 @@
         <v>+593 98 174 5020</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>4</v>
       </c>
@@ -4237,7 +4244,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>118</v>
       </c>
@@ -4252,7 +4259,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>172</v>
       </c>
@@ -4270,7 +4277,7 @@
         <v>+52 1 771 297 6010</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>177</v>
       </c>
@@ -4285,7 +4292,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>188</v>
       </c>
@@ -4303,7 +4310,7 @@
         <v>+52  1 983 752 2450</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>93</v>
       </c>
@@ -4318,7 +4325,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>153</v>
       </c>
@@ -4336,7 +4343,7 @@
         <v>+58 424-6956750</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>72</v>
       </c>
@@ -4354,7 +4361,7 @@
         <v>+51  965 337 810</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>86</v>
       </c>
@@ -4369,7 +4376,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>87</v>
       </c>
@@ -4384,7 +4391,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>75</v>
       </c>
@@ -4399,7 +4406,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>200</v>
       </c>
@@ -4414,7 +4421,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>252</v>
       </c>
@@ -4432,7 +4439,7 @@
         <v>+51  945 349 568</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>251</v>
       </c>
@@ -4450,7 +4457,7 @@
         <v>+52 1 735 162 2046</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>245</v>
       </c>
@@ -4468,7 +4475,7 @@
         <v>+51 970 857 085</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>78</v>
       </c>
@@ -4483,7 +4490,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>147</v>
       </c>
@@ -4501,7 +4508,7 @@
         <v>+52  1 673 472 3074</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>59</v>
       </c>
@@ -4519,7 +4526,7 @@
         <v>+54 9 2974 22-6785</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>241</v>
       </c>
@@ -4537,7 +4544,7 @@
         <v>+52 1 55 1805 8456</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>233</v>
       </c>
@@ -4552,7 +4559,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>35</v>
       </c>
@@ -4570,7 +4577,7 @@
         <v>+54  9 11 6135-9811</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>201</v>
       </c>
@@ -4585,7 +4592,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>218</v>
       </c>
@@ -4603,7 +4610,7 @@
         <v>+51 991 342 085</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>69</v>
       </c>
@@ -4618,7 +4625,7 @@
         <v xml:space="preserve">+506 </v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>217</v>
       </c>
@@ -4633,7 +4640,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>167</v>
       </c>
@@ -4648,7 +4655,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>256</v>
       </c>
@@ -4666,7 +4673,7 @@
         <v>+53 5 6957902</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>134</v>
       </c>
@@ -4681,7 +4688,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>132</v>
       </c>
@@ -4696,7 +4703,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>29</v>
       </c>
@@ -4714,7 +4721,7 @@
         <v>+51 977 404 957</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>53</v>
       </c>
@@ -4732,7 +4739,7 @@
         <v>+52 1 229 229 9515</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>64</v>
       </c>
@@ -4750,7 +4757,7 @@
         <v>+51 986 824 543</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>16</v>
       </c>
@@ -4768,7 +4775,7 @@
         <v>+591 69865757</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>58</v>
       </c>
@@ -4786,7 +4793,7 @@
         <v>+506  7139 5493</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>115</v>
       </c>
@@ -4801,7 +4808,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>197</v>
       </c>
@@ -4819,7 +4826,7 @@
         <v>+58 424-2233503</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>206</v>
       </c>
@@ -4837,7 +4844,7 @@
         <v>+52 6644057270</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>3</v>
       </c>
@@ -4855,7 +4862,7 @@
         <v>+51 955 121 011</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>171</v>
       </c>
@@ -4870,7 +4877,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>104</v>
       </c>
@@ -4885,7 +4892,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>152</v>
       </c>
@@ -4903,7 +4910,7 @@
         <v>+52  1 479 233 6442</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>103</v>
       </c>
@@ -4918,7 +4925,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>258</v>
       </c>
@@ -4933,7 +4940,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>80</v>
       </c>
@@ -4948,7 +4955,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>189</v>
       </c>
@@ -4966,7 +4973,7 @@
         <v>+52  1 756 103 6825</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>203</v>
       </c>
@@ -4981,7 +4988,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>173</v>
       </c>
@@ -4996,7 +5003,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>202</v>
       </c>
@@ -5014,7 +5021,7 @@
         <v>+52  1 981 217 7384</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>48</v>
       </c>
@@ -5032,7 +5039,7 @@
         <v>+52 1 231 176 9718</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>248</v>
       </c>
@@ -5047,7 +5054,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>199</v>
       </c>
@@ -5065,7 +5072,7 @@
         <v>+52  1 55 7364 9786</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>151</v>
       </c>
@@ -5080,7 +5087,7 @@
         <v xml:space="preserve">+56 </v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>182</v>
       </c>
@@ -5095,7 +5102,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>195</v>
       </c>
@@ -5113,7 +5120,7 @@
         <v>+53 5 1795768</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>96</v>
       </c>
@@ -5128,7 +5135,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>250</v>
       </c>
@@ -5146,7 +5153,7 @@
         <v>+58 414-8694655</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>97</v>
       </c>
@@ -5161,7 +5168,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>28</v>
       </c>
@@ -5179,7 +5186,7 @@
         <v>+51 981 000 049</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>190</v>
       </c>
@@ -5194,7 +5201,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>145</v>
       </c>
@@ -5212,7 +5219,7 @@
         <v>+56 9 7878 6558</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>7</v>
       </c>
@@ -5230,7 +5237,7 @@
         <v>+51 973 614 848</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>15</v>
       </c>
@@ -5248,7 +5255,7 @@
         <v>+51 971 942 638</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>237</v>
       </c>
@@ -5263,7 +5270,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>40</v>
       </c>
@@ -5281,7 +5288,7 @@
         <v>+58 422-0376517</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>91</v>
       </c>
@@ -5296,7 +5303,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>226</v>
       </c>
@@ -5314,7 +5321,7 @@
         <v>+52  1 834 252 9665</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>14</v>
       </c>
@@ -5332,7 +5339,7 @@
         <v>+506 6082 6653</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>67</v>
       </c>
@@ -5347,7 +5354,7 @@
         <v xml:space="preserve">+503 </v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>116</v>
       </c>
@@ -5362,7 +5369,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>164</v>
       </c>
@@ -5380,7 +5387,7 @@
         <v>+51 992 958 823</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>148</v>
       </c>
@@ -5398,7 +5405,7 @@
         <v>+58 412-5885303</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>98</v>
       </c>
@@ -5413,7 +5420,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>259</v>
       </c>
@@ -5428,7 +5435,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>79</v>
       </c>
@@ -5443,7 +5450,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>60</v>
       </c>
@@ -5461,7 +5468,7 @@
         <v>+58 414-7234994</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>158</v>
       </c>
@@ -5479,7 +5486,7 @@
         <v>+1 849 763-2529</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>196</v>
       </c>
@@ -5497,7 +5504,7 @@
         <v>+52 1 56 3172 0225</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>6</v>
       </c>
@@ -5512,7 +5519,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>36</v>
       </c>
@@ -5527,7 +5534,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>123</v>
       </c>
@@ -5542,7 +5549,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>73</v>
       </c>
@@ -5557,7 +5564,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>85</v>
       </c>
@@ -5572,7 +5579,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>225</v>
       </c>
@@ -5587,7 +5594,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>143</v>
       </c>
@@ -5602,7 +5609,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>219</v>
       </c>
@@ -5617,7 +5624,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>255</v>
       </c>
@@ -5635,7 +5642,7 @@
         <v>+51 923 404 224</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>81</v>
       </c>
@@ -5650,7 +5657,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>19</v>
       </c>
@@ -5668,7 +5675,7 @@
         <v>+51 987 200 136</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>13</v>
       </c>
@@ -5686,7 +5693,7 @@
         <v>+51 972691544</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>186</v>
       </c>
@@ -5704,7 +5711,7 @@
         <v>+53  5 2756474</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>204</v>
       </c>
@@ -5719,7 +5726,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>212</v>
       </c>
@@ -5734,7 +5741,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>131</v>
       </c>
@@ -5749,7 +5756,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>231</v>
       </c>
@@ -5764,7 +5771,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>76</v>
       </c>
@@ -5779,7 +5786,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>49</v>
       </c>
@@ -5794,7 +5801,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>24</v>
       </c>
@@ -5812,7 +5819,7 @@
         <v>+51 937 332 268</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>102</v>
       </c>
@@ -5830,7 +5837,7 @@
         <v>+51 955 963 610</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>170</v>
       </c>
@@ -5848,7 +5855,7 @@
         <v>+51 931 252 452</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>181</v>
       </c>
@@ -5863,7 +5870,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>82</v>
       </c>
@@ -5878,7 +5885,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1</v>
       </c>
@@ -5896,7 +5903,7 @@
         <v>+51 945 323 097</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>208</v>
       </c>
@@ -5911,7 +5918,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>63</v>
       </c>
@@ -5929,7 +5936,7 @@
         <v>+51 965 373 102</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>227</v>
       </c>
@@ -5947,7 +5954,7 @@
         <v>+52 1 916 116 9432</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>238</v>
       </c>
@@ -5965,7 +5972,7 @@
         <v>+52  1 771 112 3061</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>215</v>
       </c>
@@ -5980,7 +5987,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>70</v>
       </c>
@@ -5998,7 +6005,7 @@
         <v>+51 955 834 817</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>144</v>
       </c>
@@ -6013,7 +6020,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>95</v>
       </c>
@@ -6028,7 +6035,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>62</v>
       </c>
@@ -6046,7 +6053,7 @@
         <v>+54 9 3794 12-0368</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>11</v>
       </c>
@@ -6064,7 +6071,7 @@
         <v>+502 4760 5947</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>404</v>
       </c>
@@ -6082,7 +6089,7 @@
         <v>+57 333 2913156</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>406</v>
       </c>
@@ -6100,7 +6107,7 @@
         <v>+54 9 11 2507-8576</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>409</v>
       </c>
@@ -6115,7 +6122,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>410</v>
       </c>
@@ -6133,7 +6140,7 @@
         <v>+51  966 803 562</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>416</v>
       </c>
@@ -6151,7 +6158,7 @@
         <v>+58 412-8286364</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>418</v>
       </c>
@@ -6169,7 +6176,7 @@
         <v>+503 7279 9978</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>421</v>
       </c>
@@ -6187,14 +6194,16 @@
         <v>+51 964 533 667</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="271" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="272" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
       <c r="D272" s="1"/>
       <c r="E272" s="1"/>
       <c r="F272" s="1"/>
     </row>
-    <row r="273" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
       <c r="D273" s="2"/>
@@ -6202,7 +6211,13 @@
       <c r="F273" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E273" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}"/>
+  <autoFilter ref="A1:E273" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Eduarena"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A262">
     <sortCondition ref="A2:A262"/>
   </sortState>

--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE8A97D-064D-48FC-9391-BFB81D2F1E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6C2272-997C-4145-9A17-9A9C48707ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$273</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$269</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1324,16 +1324,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1379,17 +1371,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1704,8 +1693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:F273"/>
+  <dimension ref="A1:E269"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
@@ -1730,7 +1718,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -1745,7 +1733,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>236</v>
       </c>
@@ -1763,7 +1751,7 @@
         <v>+51 933 668 277</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>41</v>
       </c>
@@ -1781,7 +1769,7 @@
         <v>+51 980 596 555</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -1799,7 +1787,7 @@
         <v>+58 424-7086947</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>83</v>
       </c>
@@ -1814,7 +1802,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>235</v>
       </c>
@@ -1832,7 +1820,7 @@
         <v>+58 412-1322018</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>193</v>
       </c>
@@ -1850,7 +1838,7 @@
         <v>+56 9 7927 3083</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>113</v>
       </c>
@@ -1865,11 +1853,11 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>283</v>
       </c>
       <c r="C10" t="s">
@@ -1883,7 +1871,7 @@
         <v>+51 985 699 608</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -1901,7 +1889,7 @@
         <v>+52 1 56 1007 9583</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>191</v>
       </c>
@@ -1919,7 +1907,7 @@
         <v>+52 1 81 2944 2313</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>84</v>
       </c>
@@ -1934,7 +1922,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>92</v>
       </c>
@@ -1949,7 +1937,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>160</v>
       </c>
@@ -1964,7 +1952,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -1982,7 +1970,7 @@
         <v>+51  984 190 584</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>149</v>
       </c>
@@ -1997,7 +1985,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -2015,7 +2003,7 @@
         <v>+51 984 267 160</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -2033,7 +2021,7 @@
         <v>+51  912 858 811</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>127</v>
       </c>
@@ -2048,7 +2036,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>136</v>
       </c>
@@ -2066,7 +2054,7 @@
         <v>+51 949 647 819</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -2084,7 +2072,7 @@
         <v>+34  646 20 50 99</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>228</v>
       </c>
@@ -2099,7 +2087,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>137</v>
       </c>
@@ -2117,7 +2105,7 @@
         <v>+52  1 222 102 8165</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -2135,7 +2123,7 @@
         <v>+58 416-4398466</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>129</v>
       </c>
@@ -2153,7 +2141,7 @@
         <v>+54 91139028131</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -2171,7 +2159,7 @@
         <v>+57 322 4761144</v>
       </c>
     </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -2189,7 +2177,7 @@
         <v>+52 1 771 306 4084</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>234</v>
       </c>
@@ -2207,7 +2195,7 @@
         <v>+58 412-7060529</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -2225,7 +2213,7 @@
         <v>+51 933448842</v>
       </c>
     </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>37</v>
       </c>
@@ -2240,7 +2228,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -2258,7 +2246,7 @@
         <v>+51 912358537</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>179</v>
       </c>
@@ -2276,7 +2264,7 @@
         <v>+51 950 746 501</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>54</v>
       </c>
@@ -2294,7 +2282,7 @@
         <v>+54 9 3794 73 7373</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>119</v>
       </c>
@@ -2309,7 +2297,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>180</v>
       </c>
@@ -2327,11 +2315,11 @@
         <v>+55 71 9370-7438</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>254</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>377</v>
       </c>
       <c r="C37" t="s">
@@ -2345,7 +2333,7 @@
         <v>+51 991 176 689</v>
       </c>
     </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>121</v>
       </c>
@@ -2363,7 +2351,7 @@
         <v>+34 601 36 84 69</v>
       </c>
     </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>71</v>
       </c>
@@ -2378,7 +2366,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>184</v>
       </c>
@@ -2396,7 +2384,7 @@
         <v>+51  917 057 695</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>51</v>
       </c>
@@ -2414,7 +2402,7 @@
         <v>+34 608 39 51 22</v>
       </c>
     </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>221</v>
       </c>
@@ -2429,7 +2417,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>117</v>
       </c>
@@ -2444,7 +2432,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>99</v>
       </c>
@@ -2459,7 +2447,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>198</v>
       </c>
@@ -2477,7 +2465,7 @@
         <v>+54 93854880470</v>
       </c>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>61</v>
       </c>
@@ -2495,7 +2483,7 @@
         <v>+53 51162846</v>
       </c>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>169</v>
       </c>
@@ -2510,7 +2498,7 @@
         <v xml:space="preserve">+1 </v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>57</v>
       </c>
@@ -2525,7 +2513,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>10</v>
       </c>
@@ -2543,7 +2531,7 @@
         <v>+51  920 449 371</v>
       </c>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>68</v>
       </c>
@@ -2561,7 +2549,7 @@
         <v>+51  912 209 142</v>
       </c>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>105</v>
       </c>
@@ -2576,7 +2564,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>0</v>
       </c>
@@ -2594,7 +2582,7 @@
         <v>+505 8799 9543</v>
       </c>
     </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>125</v>
       </c>
@@ -2612,7 +2600,7 @@
         <v>+52 1 686 589 5829</v>
       </c>
     </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>161</v>
       </c>
@@ -2630,7 +2618,7 @@
         <v>+51 992 067 030</v>
       </c>
     </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>108</v>
       </c>
@@ -2645,7 +2633,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -2660,7 +2648,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>230</v>
       </c>
@@ -2675,7 +2663,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>32</v>
       </c>
@@ -2693,7 +2681,7 @@
         <v>+58  412-7396859</v>
       </c>
     </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>111</v>
       </c>
@@ -2711,7 +2699,7 @@
         <v>+52 1 921 208 0809</v>
       </c>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>100</v>
       </c>
@@ -2726,7 +2714,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>166</v>
       </c>
@@ -2744,7 +2732,7 @@
         <v>+504 3204-1711</v>
       </c>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>128</v>
       </c>
@@ -2762,7 +2750,7 @@
         <v>+56 99797773</v>
       </c>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>222</v>
       </c>
@@ -2777,14 +2765,14 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>39</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="1" t="s">
         <v>278</v>
       </c>
       <c r="D64">
@@ -2795,7 +2783,7 @@
         <v>+1 305 8902347</v>
       </c>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>408</v>
       </c>
@@ -2813,7 +2801,7 @@
         <v>+52 1 861 128 3193</v>
       </c>
     </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>124</v>
       </c>
@@ -2828,7 +2816,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>176</v>
       </c>
@@ -2843,7 +2831,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>216</v>
       </c>
@@ -2861,7 +2849,7 @@
         <v>+52 8341048014</v>
       </c>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>5</v>
       </c>
@@ -2879,7 +2867,7 @@
         <v>+506  8936 2350</v>
       </c>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>159</v>
       </c>
@@ -2901,7 +2889,7 @@
       <c r="A71" t="s">
         <v>74</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="2" t="s">
         <v>426</v>
       </c>
       <c r="C71" t="s">
@@ -2915,7 +2903,7 @@
         <v>+51 991 846 357</v>
       </c>
     </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>194</v>
       </c>
@@ -2933,7 +2921,7 @@
         <v>+52 1 33 4442 1918</v>
       </c>
     </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>110</v>
       </c>
@@ -2948,7 +2936,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>187</v>
       </c>
@@ -2963,7 +2951,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>240</v>
       </c>
@@ -2978,7 +2966,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>31</v>
       </c>
@@ -2996,7 +2984,7 @@
         <v>+51  912 058 374</v>
       </c>
     </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>88</v>
       </c>
@@ -3011,7 +2999,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>133</v>
       </c>
@@ -3026,7 +3014,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>90</v>
       </c>
@@ -3041,7 +3029,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>106</v>
       </c>
@@ -3056,7 +3044,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>214</v>
       </c>
@@ -3074,7 +3062,7 @@
         <v>+593  96 083 0485</v>
       </c>
     </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>112</v>
       </c>
@@ -3089,7 +3077,7 @@
         <v xml:space="preserve">+505 </v>
       </c>
     </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>107</v>
       </c>
@@ -3104,7 +3092,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>44</v>
       </c>
@@ -3122,7 +3110,7 @@
         <v>+51  983 379 394</v>
       </c>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>66</v>
       </c>
@@ -3137,7 +3125,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>162</v>
       </c>
@@ -3155,7 +3143,7 @@
         <v>+51 980 679 898</v>
       </c>
     </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>229</v>
       </c>
@@ -3170,7 +3158,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>139</v>
       </c>
@@ -3188,7 +3176,7 @@
         <v>+53  5 6467775</v>
       </c>
     </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>175</v>
       </c>
@@ -3206,7 +3194,7 @@
         <v>+51 943126988</v>
       </c>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>122</v>
       </c>
@@ -3221,7 +3209,7 @@
         <v xml:space="preserve">+593 </v>
       </c>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>213</v>
       </c>
@@ -3236,7 +3224,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>45</v>
       </c>
@@ -3254,7 +3242,7 @@
         <v>+54 9 3412 81-3587</v>
       </c>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>89</v>
       </c>
@@ -3269,7 +3257,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>120</v>
       </c>
@@ -3287,7 +3275,7 @@
         <v>+57  302 5578252</v>
       </c>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>205</v>
       </c>
@@ -3305,7 +3293,7 @@
         <v>+593 96 151 5565</v>
       </c>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>243</v>
       </c>
@@ -3323,7 +3311,7 @@
         <v>+51 956 677 392</v>
       </c>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>239</v>
       </c>
@@ -3341,7 +3329,7 @@
         <v>+54 9 11 2783 9968</v>
       </c>
     </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>155</v>
       </c>
@@ -3359,7 +3347,7 @@
         <v>+51 961 492 733</v>
       </c>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>34</v>
       </c>
@@ -3377,7 +3365,7 @@
         <v>+53 5 1113536</v>
       </c>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>140</v>
       </c>
@@ -3392,7 +3380,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>232</v>
       </c>
@@ -3407,7 +3395,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>141</v>
       </c>
@@ -3422,7 +3410,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>55</v>
       </c>
@@ -3440,7 +3428,7 @@
         <v>+1 809 658-5500</v>
       </c>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>154</v>
       </c>
@@ -3458,7 +3446,7 @@
         <v>+58 424-1216695</v>
       </c>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>168</v>
       </c>
@@ -3476,7 +3464,7 @@
         <v>+51 963 745 855</v>
       </c>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>224</v>
       </c>
@@ -3494,7 +3482,7 @@
         <v>+51  960 274 071</v>
       </c>
     </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>114</v>
       </c>
@@ -3512,7 +3500,7 @@
         <v>+593 98 768 2900</v>
       </c>
     </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>94</v>
       </c>
@@ -3527,7 +3515,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>246</v>
       </c>
@@ -3545,7 +3533,7 @@
         <v>+503 7868 0662</v>
       </c>
     </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>242</v>
       </c>
@@ -3560,7 +3548,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>156</v>
       </c>
@@ -3578,7 +3566,7 @@
         <v>+58 414-4473628</v>
       </c>
     </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>43</v>
       </c>
@@ -3596,7 +3584,7 @@
         <v>+57 3054850698</v>
       </c>
     </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>223</v>
       </c>
@@ -3611,7 +3599,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>163</v>
       </c>
@@ -3626,7 +3614,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>56</v>
       </c>
@@ -3641,7 +3629,7 @@
         <v xml:space="preserve">+507 </v>
       </c>
     </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>150</v>
       </c>
@@ -3659,7 +3647,7 @@
         <v>+58  412-1885430</v>
       </c>
     </row>
-    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>130</v>
       </c>
@@ -3677,7 +3665,7 @@
         <v>+51  906 691 465</v>
       </c>
     </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>146</v>
       </c>
@@ -3692,7 +3680,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>165</v>
       </c>
@@ -3710,7 +3698,7 @@
         <v>+1  787 513-4231</v>
       </c>
     </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>46</v>
       </c>
@@ -3728,7 +3716,7 @@
         <v>+507  6898-7574</v>
       </c>
     </row>
-    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>209</v>
       </c>
@@ -3746,7 +3734,7 @@
         <v>+52 1 444 674 9780</v>
       </c>
     </row>
-    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>2</v>
       </c>
@@ -3761,11 +3749,11 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>21</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B123" s="2" t="s">
         <v>331</v>
       </c>
       <c r="C123" t="s">
@@ -3779,7 +3767,7 @@
         <v>+51 996 668 615</v>
       </c>
     </row>
-    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>77</v>
       </c>
@@ -3794,7 +3782,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>249</v>
       </c>
@@ -3812,7 +3800,7 @@
         <v>+52 1 55 3845 6274</v>
       </c>
     </row>
-    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>192</v>
       </c>
@@ -3827,7 +3815,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>253</v>
       </c>
@@ -3845,11 +3833,11 @@
         <v>+51  921 447 908</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>12</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="B128" s="2" t="s">
         <v>369</v>
       </c>
       <c r="C128" t="s">
@@ -3863,7 +3851,7 @@
         <v>+51 976 413 331</v>
       </c>
     </row>
-    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>183</v>
       </c>
@@ -3878,7 +3866,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>101</v>
       </c>
@@ -3893,7 +3881,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>157</v>
       </c>
@@ -3908,7 +3896,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>47</v>
       </c>
@@ -3923,7 +3911,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>220</v>
       </c>
@@ -3941,7 +3929,7 @@
         <v>+52 Juni Frostheart</v>
       </c>
     </row>
-    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>257</v>
       </c>
@@ -3959,7 +3947,7 @@
         <v>+54 9 11 2526 8333</v>
       </c>
     </row>
-    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>247</v>
       </c>
@@ -3977,7 +3965,7 @@
         <v>+51 963 347 387</v>
       </c>
     </row>
-    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>33</v>
       </c>
@@ -3995,7 +3983,7 @@
         <v>+52 1 81 2684 3183</v>
       </c>
     </row>
-    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>135</v>
       </c>
@@ -4010,7 +3998,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>178</v>
       </c>
@@ -4025,7 +4013,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>109</v>
       </c>
@@ -4040,7 +4028,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>142</v>
       </c>
@@ -4055,11 +4043,11 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>26</v>
       </c>
-      <c r="B141" s="3" t="s">
+      <c r="B141" s="2" t="s">
         <v>334</v>
       </c>
       <c r="C141" t="s">
@@ -4073,7 +4061,7 @@
         <v>+57 302 3773516</v>
       </c>
     </row>
-    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -4091,11 +4079,11 @@
         <v>+54  9 11 2372-2211</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>211</v>
       </c>
-      <c r="B143" s="3" t="s">
+      <c r="B143" s="2" t="s">
         <v>336</v>
       </c>
       <c r="C143" t="s">
@@ -4109,7 +4097,7 @@
         <v>+51 960 749 072</v>
       </c>
     </row>
-    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>25</v>
       </c>
@@ -4127,7 +4115,7 @@
         <v>+51 984 784 816</v>
       </c>
     </row>
-    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>244</v>
       </c>
@@ -4145,7 +4133,7 @@
         <v>+51 986 579 683</v>
       </c>
     </row>
-    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>207</v>
       </c>
@@ -4163,7 +4151,7 @@
         <v>+52 1 614 529 6392</v>
       </c>
     </row>
-    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>210</v>
       </c>
@@ -4181,7 +4169,7 @@
         <v>+52 1 287 154 7879</v>
       </c>
     </row>
-    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>174</v>
       </c>
@@ -4196,7 +4184,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>185</v>
       </c>
@@ -4211,7 +4199,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>65</v>
       </c>
@@ -4221,7 +4209,7 @@
       <c r="C150" t="s">
         <v>314</v>
       </c>
-      <c r="D150" s="4">
+      <c r="D150" s="3">
         <v>593</v>
       </c>
       <c r="E150" t="str">
@@ -4229,7 +4217,7 @@
         <v>+593 98 174 5020</v>
       </c>
     </row>
-    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>4</v>
       </c>
@@ -4244,7 +4232,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>118</v>
       </c>
@@ -4259,7 +4247,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>172</v>
       </c>
@@ -4277,7 +4265,7 @@
         <v>+52 1 771 297 6010</v>
       </c>
     </row>
-    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>177</v>
       </c>
@@ -4292,7 +4280,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>188</v>
       </c>
@@ -4310,7 +4298,7 @@
         <v>+52  1 983 752 2450</v>
       </c>
     </row>
-    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>93</v>
       </c>
@@ -4325,7 +4313,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>153</v>
       </c>
@@ -4343,7 +4331,7 @@
         <v>+58 424-6956750</v>
       </c>
     </row>
-    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>72</v>
       </c>
@@ -4361,7 +4349,7 @@
         <v>+51  965 337 810</v>
       </c>
     </row>
-    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>86</v>
       </c>
@@ -4376,7 +4364,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>87</v>
       </c>
@@ -4391,7 +4379,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>75</v>
       </c>
@@ -4406,7 +4394,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>200</v>
       </c>
@@ -4421,7 +4409,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>252</v>
       </c>
@@ -4439,7 +4427,7 @@
         <v>+51  945 349 568</v>
       </c>
     </row>
-    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>251</v>
       </c>
@@ -4457,11 +4445,11 @@
         <v>+52 1 735 162 2046</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>245</v>
       </c>
-      <c r="B165" s="3" t="s">
+      <c r="B165" s="2" t="s">
         <v>338</v>
       </c>
       <c r="C165" t="s">
@@ -4475,7 +4463,7 @@
         <v>+51 970 857 085</v>
       </c>
     </row>
-    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>78</v>
       </c>
@@ -4490,7 +4478,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>147</v>
       </c>
@@ -4508,7 +4496,7 @@
         <v>+52  1 673 472 3074</v>
       </c>
     </row>
-    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>59</v>
       </c>
@@ -4526,7 +4514,7 @@
         <v>+54 9 2974 22-6785</v>
       </c>
     </row>
-    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>241</v>
       </c>
@@ -4544,7 +4532,7 @@
         <v>+52 1 55 1805 8456</v>
       </c>
     </row>
-    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>233</v>
       </c>
@@ -4559,7 +4547,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>35</v>
       </c>
@@ -4577,7 +4565,7 @@
         <v>+54  9 11 6135-9811</v>
       </c>
     </row>
-    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>201</v>
       </c>
@@ -4592,11 +4580,11 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>218</v>
       </c>
-      <c r="B173" s="3" t="s">
+      <c r="B173" s="2" t="s">
         <v>341</v>
       </c>
       <c r="C173" t="s">
@@ -4610,7 +4598,7 @@
         <v>+51 991 342 085</v>
       </c>
     </row>
-    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>69</v>
       </c>
@@ -4625,7 +4613,7 @@
         <v xml:space="preserve">+506 </v>
       </c>
     </row>
-    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>217</v>
       </c>
@@ -4640,7 +4628,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>167</v>
       </c>
@@ -4655,7 +4643,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>256</v>
       </c>
@@ -4673,7 +4661,7 @@
         <v>+53 5 6957902</v>
       </c>
     </row>
-    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>134</v>
       </c>
@@ -4688,7 +4676,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>132</v>
       </c>
@@ -4703,11 +4691,11 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>29</v>
       </c>
-      <c r="B180" s="3" t="s">
+      <c r="B180" s="2" t="s">
         <v>342</v>
       </c>
       <c r="C180" t="s">
@@ -4721,7 +4709,7 @@
         <v>+51 977 404 957</v>
       </c>
     </row>
-    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>53</v>
       </c>
@@ -4739,11 +4727,11 @@
         <v>+52 1 229 229 9515</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>64</v>
       </c>
-      <c r="B182" s="3" t="s">
+      <c r="B182" s="2" t="s">
         <v>345</v>
       </c>
       <c r="C182" t="s">
@@ -4757,7 +4745,7 @@
         <v>+51 986 824 543</v>
       </c>
     </row>
-    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>16</v>
       </c>
@@ -4775,7 +4763,7 @@
         <v>+591 69865757</v>
       </c>
     </row>
-    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>58</v>
       </c>
@@ -4793,7 +4781,7 @@
         <v>+506  7139 5493</v>
       </c>
     </row>
-    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>115</v>
       </c>
@@ -4808,7 +4796,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>197</v>
       </c>
@@ -4826,7 +4814,7 @@
         <v>+58 424-2233503</v>
       </c>
     </row>
-    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>206</v>
       </c>
@@ -4844,7 +4832,7 @@
         <v>+52 6644057270</v>
       </c>
     </row>
-    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>3</v>
       </c>
@@ -4862,7 +4850,7 @@
         <v>+51 955 121 011</v>
       </c>
     </row>
-    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>171</v>
       </c>
@@ -4877,7 +4865,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>104</v>
       </c>
@@ -4892,7 +4880,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>152</v>
       </c>
@@ -4910,7 +4898,7 @@
         <v>+52  1 479 233 6442</v>
       </c>
     </row>
-    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>103</v>
       </c>
@@ -4925,7 +4913,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>258</v>
       </c>
@@ -4940,7 +4928,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>80</v>
       </c>
@@ -4955,7 +4943,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>189</v>
       </c>
@@ -4973,7 +4961,7 @@
         <v>+52  1 756 103 6825</v>
       </c>
     </row>
-    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>203</v>
       </c>
@@ -4988,7 +4976,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>173</v>
       </c>
@@ -5003,7 +4991,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>202</v>
       </c>
@@ -5021,7 +5009,7 @@
         <v>+52  1 981 217 7384</v>
       </c>
     </row>
-    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>48</v>
       </c>
@@ -5039,7 +5027,7 @@
         <v>+52 1 231 176 9718</v>
       </c>
     </row>
-    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>248</v>
       </c>
@@ -5054,7 +5042,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>199</v>
       </c>
@@ -5072,7 +5060,7 @@
         <v>+52  1 55 7364 9786</v>
       </c>
     </row>
-    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>151</v>
       </c>
@@ -5087,7 +5075,7 @@
         <v xml:space="preserve">+56 </v>
       </c>
     </row>
-    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>182</v>
       </c>
@@ -5102,7 +5090,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>195</v>
       </c>
@@ -5120,7 +5108,7 @@
         <v>+53 5 1795768</v>
       </c>
     </row>
-    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>96</v>
       </c>
@@ -5135,7 +5123,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>250</v>
       </c>
@@ -5153,7 +5141,7 @@
         <v>+58 414-8694655</v>
       </c>
     </row>
-    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>97</v>
       </c>
@@ -5168,7 +5156,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>28</v>
       </c>
@@ -5186,7 +5174,7 @@
         <v>+51 981 000 049</v>
       </c>
     </row>
-    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>190</v>
       </c>
@@ -5201,7 +5189,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>145</v>
       </c>
@@ -5219,7 +5207,7 @@
         <v>+56 9 7878 6558</v>
       </c>
     </row>
-    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>7</v>
       </c>
@@ -5237,7 +5225,7 @@
         <v>+51 973 614 848</v>
       </c>
     </row>
-    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>15</v>
       </c>
@@ -5255,7 +5243,7 @@
         <v>+51 971 942 638</v>
       </c>
     </row>
-    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>237</v>
       </c>
@@ -5270,7 +5258,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>40</v>
       </c>
@@ -5288,7 +5276,7 @@
         <v>+58 422-0376517</v>
       </c>
     </row>
-    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>91</v>
       </c>
@@ -5303,7 +5291,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>226</v>
       </c>
@@ -5321,7 +5309,7 @@
         <v>+52  1 834 252 9665</v>
       </c>
     </row>
-    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>14</v>
       </c>
@@ -5339,7 +5327,7 @@
         <v>+506 6082 6653</v>
       </c>
     </row>
-    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>67</v>
       </c>
@@ -5354,7 +5342,7 @@
         <v xml:space="preserve">+503 </v>
       </c>
     </row>
-    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>116</v>
       </c>
@@ -5369,11 +5357,11 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>164</v>
       </c>
-      <c r="B220" s="3" t="s">
+      <c r="B220" s="2" t="s">
         <v>424</v>
       </c>
       <c r="C220" t="s">
@@ -5387,7 +5375,7 @@
         <v>+51 992 958 823</v>
       </c>
     </row>
-    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>148</v>
       </c>
@@ -5405,7 +5393,7 @@
         <v>+58 412-5885303</v>
       </c>
     </row>
-    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>98</v>
       </c>
@@ -5420,7 +5408,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>259</v>
       </c>
@@ -5435,7 +5423,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>79</v>
       </c>
@@ -5450,7 +5438,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>60</v>
       </c>
@@ -5468,7 +5456,7 @@
         <v>+58 414-7234994</v>
       </c>
     </row>
-    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>158</v>
       </c>
@@ -5486,7 +5474,7 @@
         <v>+1 849 763-2529</v>
       </c>
     </row>
-    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>196</v>
       </c>
@@ -5504,7 +5492,7 @@
         <v>+52 1 56 3172 0225</v>
       </c>
     </row>
-    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>6</v>
       </c>
@@ -5519,7 +5507,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>36</v>
       </c>
@@ -5534,7 +5522,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>123</v>
       </c>
@@ -5549,7 +5537,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>73</v>
       </c>
@@ -5564,7 +5552,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>85</v>
       </c>
@@ -5579,7 +5567,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>225</v>
       </c>
@@ -5594,7 +5582,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>143</v>
       </c>
@@ -5609,7 +5597,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>219</v>
       </c>
@@ -5624,7 +5612,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>255</v>
       </c>
@@ -5642,7 +5630,7 @@
         <v>+51 923 404 224</v>
       </c>
     </row>
-    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>81</v>
       </c>
@@ -5657,7 +5645,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>19</v>
       </c>
@@ -5675,7 +5663,7 @@
         <v>+51 987 200 136</v>
       </c>
     </row>
-    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>13</v>
       </c>
@@ -5693,7 +5681,7 @@
         <v>+51 972691544</v>
       </c>
     </row>
-    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>186</v>
       </c>
@@ -5711,7 +5699,7 @@
         <v>+53  5 2756474</v>
       </c>
     </row>
-    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>204</v>
       </c>
@@ -5726,7 +5714,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>212</v>
       </c>
@@ -5741,7 +5729,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>131</v>
       </c>
@@ -5756,7 +5744,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>231</v>
       </c>
@@ -5771,7 +5759,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>76</v>
       </c>
@@ -5786,7 +5774,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>49</v>
       </c>
@@ -5801,7 +5789,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>24</v>
       </c>
@@ -5819,7 +5807,7 @@
         <v>+51 937 332 268</v>
       </c>
     </row>
-    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>102</v>
       </c>
@@ -5837,7 +5825,7 @@
         <v>+51 955 963 610</v>
       </c>
     </row>
-    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>170</v>
       </c>
@@ -5855,7 +5843,7 @@
         <v>+51 931 252 452</v>
       </c>
     </row>
-    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>181</v>
       </c>
@@ -5870,7 +5858,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>82</v>
       </c>
@@ -5885,7 +5873,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1</v>
       </c>
@@ -5903,7 +5891,7 @@
         <v>+51 945 323 097</v>
       </c>
     </row>
-    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>208</v>
       </c>
@@ -5918,7 +5906,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>63</v>
       </c>
@@ -5936,7 +5924,7 @@
         <v>+51 965 373 102</v>
       </c>
     </row>
-    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>227</v>
       </c>
@@ -5954,7 +5942,7 @@
         <v>+52 1 916 116 9432</v>
       </c>
     </row>
-    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>238</v>
       </c>
@@ -5972,7 +5960,7 @@
         <v>+52  1 771 112 3061</v>
       </c>
     </row>
-    <row r="257" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>215</v>
       </c>
@@ -5987,7 +5975,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="258" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>70</v>
       </c>
@@ -6005,7 +5993,7 @@
         <v>+51 955 834 817</v>
       </c>
     </row>
-    <row r="259" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>144</v>
       </c>
@@ -6020,7 +6008,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>95</v>
       </c>
@@ -6035,7 +6023,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="261" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>62</v>
       </c>
@@ -6053,7 +6041,7 @@
         <v>+54 9 3794 12-0368</v>
       </c>
     </row>
-    <row r="262" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>11</v>
       </c>
@@ -6071,7 +6059,7 @@
         <v>+502 4760 5947</v>
       </c>
     </row>
-    <row r="263" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>404</v>
       </c>
@@ -6089,7 +6077,7 @@
         <v>+57 333 2913156</v>
       </c>
     </row>
-    <row r="264" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>406</v>
       </c>
@@ -6107,7 +6095,7 @@
         <v>+54 9 11 2507-8576</v>
       </c>
     </row>
-    <row r="265" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>409</v>
       </c>
@@ -6122,7 +6110,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="266" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>410</v>
       </c>
@@ -6140,7 +6128,7 @@
         <v>+51  966 803 562</v>
       </c>
     </row>
-    <row r="267" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>416</v>
       </c>
@@ -6158,7 +6146,7 @@
         <v>+58 412-8286364</v>
       </c>
     </row>
-    <row r="268" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>418</v>
       </c>
@@ -6176,11 +6164,11 @@
         <v>+503 7279 9978</v>
       </c>
     </row>
-    <row r="269" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>421</v>
       </c>
-      <c r="B269" s="5" t="s">
+      <c r="B269" s="4" t="s">
         <v>420</v>
       </c>
       <c r="C269" t="s">
@@ -6194,30 +6182,8 @@
         <v>+51 964 533 667</v>
       </c>
     </row>
-    <row r="270" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="271" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="272" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B272" s="1"/>
-      <c r="C272" s="1"/>
-      <c r="D272" s="1"/>
-      <c r="E272" s="1"/>
-      <c r="F272" s="1"/>
-    </row>
-    <row r="273" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B273" s="2"/>
-      <c r="C273" s="2"/>
-      <c r="D273" s="2"/>
-      <c r="E273" s="2"/>
-      <c r="F273" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E273" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Eduarena"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:E269" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A262">
     <sortCondition ref="A2:A262"/>
   </sortState>

--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6C2272-997C-4145-9A17-9A9C48707ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DF062A-B395-410E-981E-0477E725E9DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
@@ -579,9 +579,6 @@
     <t>Car10seduard0</t>
   </si>
   <si>
-    <t>CauÃ£</t>
-  </si>
-  <si>
     <t>XrisPG</t>
   </si>
   <si>
@@ -1318,6 +1315,9 @@
   </si>
   <si>
     <t>991 846 357</t>
+  </si>
+  <si>
+    <t>Caua</t>
   </si>
 </sst>
 </file>
@@ -1703,19 +1703,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B1" t="s">
         <v>260</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>261</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>263</v>
+      </c>
+      <c r="E1" t="s">
         <v>262</v>
-      </c>
-      <c r="D1" t="s">
-        <v>264</v>
-      </c>
-      <c r="E1" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1723,7 +1723,7 @@
         <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D2">
         <v>51</v>
@@ -1735,13 +1735,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D3">
         <v>51</v>
@@ -1756,10 +1756,10 @@
         <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D4">
         <v>51</v>
@@ -1774,10 +1774,10 @@
         <v>38</v>
       </c>
       <c r="B5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D5">
         <v>58</v>
@@ -1792,7 +1792,7 @@
         <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D6">
         <v>51</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D7">
         <v>58</v>
@@ -1822,13 +1822,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B8" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D8">
         <v>56</v>
@@ -1843,7 +1843,7 @@
         <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D9">
         <v>52</v>
@@ -1858,10 +1858,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D10">
         <v>51</v>
@@ -1876,10 +1876,10 @@
         <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D11">
         <v>52</v>
@@ -1891,13 +1891,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D12">
         <v>52</v>
@@ -1912,7 +1912,7 @@
         <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D13">
         <v>51</v>
@@ -1927,7 +1927,7 @@
         <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D14">
         <v>51</v>
@@ -1942,7 +1942,7 @@
         <v>160</v>
       </c>
       <c r="C15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D15">
         <v>51</v>
@@ -1957,10 +1957,10 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C16" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D16">
         <v>51</v>
@@ -1975,7 +1975,7 @@
         <v>149</v>
       </c>
       <c r="C17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D17">
         <v>57</v>
@@ -1990,10 +1990,10 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C18" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D18">
         <v>51</v>
@@ -2008,10 +2008,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C19" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D19">
         <v>51</v>
@@ -2026,7 +2026,7 @@
         <v>127</v>
       </c>
       <c r="C20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D20">
         <v>51</v>
@@ -2041,10 +2041,10 @@
         <v>136</v>
       </c>
       <c r="B21" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D21">
         <v>51</v>
@@ -2059,10 +2059,10 @@
         <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C22" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D22">
         <v>34</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C23" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D23">
         <v>51</v>
@@ -2092,10 +2092,10 @@
         <v>137</v>
       </c>
       <c r="B24" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C24" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D24">
         <v>52</v>
@@ -2110,10 +2110,10 @@
         <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C25" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D25">
         <v>58</v>
@@ -2131,7 +2131,7 @@
         <v>91139028131</v>
       </c>
       <c r="C26" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D26">
         <v>54</v>
@@ -2146,10 +2146,10 @@
         <v>138</v>
       </c>
       <c r="B27" t="s">
+        <v>291</v>
+      </c>
+      <c r="C27" t="s">
         <v>292</v>
-      </c>
-      <c r="C27" t="s">
-        <v>293</v>
       </c>
       <c r="D27">
         <v>57</v>
@@ -2164,10 +2164,10 @@
         <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C28" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D28">
         <v>52</v>
@@ -2179,13 +2179,13 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C29" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D29">
         <v>58</v>
@@ -2203,7 +2203,7 @@
         <v>933448842</v>
       </c>
       <c r="C30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D30">
         <v>51</v>
@@ -2218,7 +2218,7 @@
         <v>37</v>
       </c>
       <c r="C31" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D31">
         <v>51</v>
@@ -2236,7 +2236,7 @@
         <v>912358537</v>
       </c>
       <c r="C32" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D32">
         <v>51</v>
@@ -2251,10 +2251,10 @@
         <v>179</v>
       </c>
       <c r="B33" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C33" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D33">
         <v>51</v>
@@ -2269,10 +2269,10 @@
         <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C34" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D34">
         <v>54</v>
@@ -2287,7 +2287,7 @@
         <v>119</v>
       </c>
       <c r="C35" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D35">
         <v>52</v>
@@ -2299,13 +2299,13 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>180</v>
+        <v>426</v>
       </c>
       <c r="B36" t="s">
+        <v>295</v>
+      </c>
+      <c r="C36" t="s">
         <v>296</v>
-      </c>
-      <c r="C36" t="s">
-        <v>297</v>
       </c>
       <c r="D36">
         <v>55</v>
@@ -2317,13 +2317,13 @@
     </row>
     <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C37" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D37">
         <v>51</v>
@@ -2338,10 +2338,10 @@
         <v>121</v>
       </c>
       <c r="B38" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C38" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D38">
         <v>34</v>
@@ -2356,7 +2356,7 @@
         <v>71</v>
       </c>
       <c r="C39" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D39">
         <v>51</v>
@@ -2368,13 +2368,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B40" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C40" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D40">
         <v>51</v>
@@ -2389,10 +2389,10 @@
         <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C41" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D41">
         <v>34</v>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C42" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D42">
         <v>51</v>
@@ -2422,7 +2422,7 @@
         <v>117</v>
       </c>
       <c r="C43" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D43">
         <v>51</v>
@@ -2437,7 +2437,7 @@
         <v>99</v>
       </c>
       <c r="C44" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D44">
         <v>51</v>
@@ -2449,13 +2449,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B45">
         <v>93854880470</v>
       </c>
       <c r="C45" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D45">
         <v>54</v>
@@ -2473,7 +2473,7 @@
         <v>51162846</v>
       </c>
       <c r="C46" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D46">
         <v>53</v>
@@ -2488,7 +2488,7 @@
         <v>169</v>
       </c>
       <c r="C47" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -2503,7 +2503,7 @@
         <v>57</v>
       </c>
       <c r="C48" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D48">
         <v>58</v>
@@ -2518,10 +2518,10 @@
         <v>10</v>
       </c>
       <c r="B49" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C49" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D49">
         <v>51</v>
@@ -2536,10 +2536,10 @@
         <v>68</v>
       </c>
       <c r="B50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C50" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D50">
         <v>51</v>
@@ -2554,7 +2554,7 @@
         <v>105</v>
       </c>
       <c r="C51" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D51">
         <v>51</v>
@@ -2569,10 +2569,10 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
+        <v>303</v>
+      </c>
+      <c r="C52" t="s">
         <v>304</v>
-      </c>
-      <c r="C52" t="s">
-        <v>305</v>
       </c>
       <c r="D52">
         <v>505</v>
@@ -2587,10 +2587,10 @@
         <v>125</v>
       </c>
       <c r="B53" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C53" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -2605,10 +2605,10 @@
         <v>161</v>
       </c>
       <c r="B54" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C54" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D54">
         <v>51</v>
@@ -2623,7 +2623,7 @@
         <v>108</v>
       </c>
       <c r="C55" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D55">
         <v>57</v>
@@ -2638,7 +2638,7 @@
         <v>9</v>
       </c>
       <c r="C56" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D56">
         <v>51</v>
@@ -2650,10 +2650,10 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C57" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D57">
         <v>58</v>
@@ -2668,10 +2668,10 @@
         <v>32</v>
       </c>
       <c r="B58" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C58" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D58">
         <v>58</v>
@@ -2686,10 +2686,10 @@
         <v>111</v>
       </c>
       <c r="B59" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C59" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D59">
         <v>52</v>
@@ -2704,7 +2704,7 @@
         <v>100</v>
       </c>
       <c r="C60" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D60">
         <v>51</v>
@@ -2719,10 +2719,10 @@
         <v>166</v>
       </c>
       <c r="B61" t="s">
+        <v>374</v>
+      </c>
+      <c r="C61" t="s">
         <v>375</v>
-      </c>
-      <c r="C61" t="s">
-        <v>376</v>
       </c>
       <c r="D61">
         <v>504</v>
@@ -2740,7 +2740,7 @@
         <v>99797773</v>
       </c>
       <c r="C62" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D62">
         <v>56</v>
@@ -2752,10 +2752,10 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C63" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D63">
         <v>51</v>
@@ -2770,10 +2770,10 @@
         <v>39</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>278</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -2785,13 +2785,13 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B65" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C65" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D65">
         <v>52</v>
@@ -2806,7 +2806,7 @@
         <v>124</v>
       </c>
       <c r="C66" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D66">
         <v>58</v>
@@ -2821,7 +2821,7 @@
         <v>176</v>
       </c>
       <c r="C67" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D67">
         <v>58</v>
@@ -2833,13 +2833,13 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B68">
         <v>8341048014</v>
       </c>
       <c r="C68" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D68">
         <v>52</v>
@@ -2854,10 +2854,10 @@
         <v>5</v>
       </c>
       <c r="B69" t="s">
+        <v>309</v>
+      </c>
+      <c r="C69" t="s">
         <v>310</v>
-      </c>
-      <c r="C69" t="s">
-        <v>311</v>
       </c>
       <c r="D69">
         <v>506</v>
@@ -2872,10 +2872,10 @@
         <v>159</v>
       </c>
       <c r="B70" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C70" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -2890,10 +2890,10 @@
         <v>74</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C71" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D71">
         <v>51</v>
@@ -2905,13 +2905,13 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B72" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C72" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D72">
         <v>52</v>
@@ -2926,7 +2926,7 @@
         <v>110</v>
       </c>
       <c r="C73" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D73">
         <v>51</v>
@@ -2938,10 +2938,10 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C74" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D74">
         <v>57</v>
@@ -2953,10 +2953,10 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C75" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D75">
         <v>54</v>
@@ -2971,10 +2971,10 @@
         <v>31</v>
       </c>
       <c r="B76" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C76" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D76">
         <v>51</v>
@@ -2989,7 +2989,7 @@
         <v>88</v>
       </c>
       <c r="C77" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D77">
         <v>51</v>
@@ -3004,7 +3004,7 @@
         <v>133</v>
       </c>
       <c r="C78" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D78">
         <v>58</v>
@@ -3019,7 +3019,7 @@
         <v>90</v>
       </c>
       <c r="C79" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D79">
         <v>51</v>
@@ -3034,7 +3034,7 @@
         <v>106</v>
       </c>
       <c r="C80" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D80">
         <v>52</v>
@@ -3046,13 +3046,13 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B81" t="s">
+        <v>312</v>
+      </c>
+      <c r="C81" t="s">
         <v>313</v>
-      </c>
-      <c r="C81" t="s">
-        <v>314</v>
       </c>
       <c r="D81">
         <v>593</v>
@@ -3067,7 +3067,7 @@
         <v>112</v>
       </c>
       <c r="C82" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D82">
         <v>505</v>
@@ -3082,7 +3082,7 @@
         <v>107</v>
       </c>
       <c r="C83" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D83">
         <v>52</v>
@@ -3097,10 +3097,10 @@
         <v>44</v>
       </c>
       <c r="B84" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C84" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D84">
         <v>51</v>
@@ -3115,7 +3115,7 @@
         <v>66</v>
       </c>
       <c r="C85" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D85">
         <v>54</v>
@@ -3130,10 +3130,10 @@
         <v>162</v>
       </c>
       <c r="B86" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C86" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D86">
         <v>51</v>
@@ -3145,10 +3145,10 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D87">
         <v>54</v>
@@ -3163,10 +3163,10 @@
         <v>139</v>
       </c>
       <c r="B88" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C88" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D88">
         <v>53</v>
@@ -3184,7 +3184,7 @@
         <v>943126988</v>
       </c>
       <c r="C89" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D89">
         <v>51</v>
@@ -3199,7 +3199,7 @@
         <v>122</v>
       </c>
       <c r="C90" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D90">
         <v>593</v>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C91" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D91">
         <v>52</v>
@@ -3229,10 +3229,10 @@
         <v>45</v>
       </c>
       <c r="B92" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C92" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D92">
         <v>54</v>
@@ -3247,7 +3247,7 @@
         <v>89</v>
       </c>
       <c r="C93" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D93">
         <v>51</v>
@@ -3262,10 +3262,10 @@
         <v>120</v>
       </c>
       <c r="B94" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C94" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D94">
         <v>57</v>
@@ -3277,13 +3277,13 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B95" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C95" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D95">
         <v>593</v>
@@ -3295,13 +3295,13 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B96" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C96" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D96">
         <v>51</v>
@@ -3313,13 +3313,13 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B97" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C97" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D97">
         <v>54</v>
@@ -3334,10 +3334,10 @@
         <v>155</v>
       </c>
       <c r="B98" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C98" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D98">
         <v>51</v>
@@ -3352,10 +3352,10 @@
         <v>34</v>
       </c>
       <c r="B99" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C99" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D99">
         <v>53</v>
@@ -3370,7 +3370,7 @@
         <v>140</v>
       </c>
       <c r="C100" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D100">
         <v>54</v>
@@ -3382,10 +3382,10 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C101" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D101">
         <v>54</v>
@@ -3400,7 +3400,7 @@
         <v>141</v>
       </c>
       <c r="C102" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D102">
         <v>57</v>
@@ -3415,10 +3415,10 @@
         <v>55</v>
       </c>
       <c r="B103" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C103" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -3433,10 +3433,10 @@
         <v>154</v>
       </c>
       <c r="B104" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C104" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D104">
         <v>58</v>
@@ -3451,10 +3451,10 @@
         <v>168</v>
       </c>
       <c r="B105" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C105" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D105">
         <v>51</v>
@@ -3466,13 +3466,13 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B106" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C106" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D106">
         <v>51</v>
@@ -3487,10 +3487,10 @@
         <v>114</v>
       </c>
       <c r="B107" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C107" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D107">
         <v>593</v>
@@ -3505,7 +3505,7 @@
         <v>94</v>
       </c>
       <c r="C108" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D108">
         <v>52</v>
@@ -3517,13 +3517,13 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B109" t="s">
+        <v>379</v>
+      </c>
+      <c r="C109" t="s">
         <v>380</v>
-      </c>
-      <c r="C109" t="s">
-        <v>381</v>
       </c>
       <c r="D109">
         <v>503</v>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C110" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D110">
         <v>51</v>
@@ -3553,10 +3553,10 @@
         <v>156</v>
       </c>
       <c r="B111" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C111" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D111">
         <v>58</v>
@@ -3574,7 +3574,7 @@
         <v>3054850698</v>
       </c>
       <c r="C112" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D112">
         <v>57</v>
@@ -3586,10 +3586,10 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C113" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D113">
         <v>51</v>
@@ -3604,7 +3604,7 @@
         <v>163</v>
       </c>
       <c r="C114" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D114">
         <v>51</v>
@@ -3619,7 +3619,7 @@
         <v>56</v>
       </c>
       <c r="C115" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D115">
         <v>507</v>
@@ -3634,10 +3634,10 @@
         <v>150</v>
       </c>
       <c r="B116" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C116" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D116">
         <v>58</v>
@@ -3652,10 +3652,10 @@
         <v>130</v>
       </c>
       <c r="B117" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C117" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D117">
         <v>51</v>
@@ -3670,7 +3670,7 @@
         <v>146</v>
       </c>
       <c r="C118" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D118">
         <v>51</v>
@@ -3685,10 +3685,10 @@
         <v>165</v>
       </c>
       <c r="B119" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C119" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -3703,10 +3703,10 @@
         <v>46</v>
       </c>
       <c r="B120" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C120" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D120">
         <v>507</v>
@@ -3718,13 +3718,13 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B121" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C121" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D121">
         <v>52</v>
@@ -3739,7 +3739,7 @@
         <v>2</v>
       </c>
       <c r="C122" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D122">
         <v>51</v>
@@ -3754,10 +3754,10 @@
         <v>21</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C123" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D123">
         <v>51</v>
@@ -3772,7 +3772,7 @@
         <v>77</v>
       </c>
       <c r="C124" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D124">
         <v>51</v>
@@ -3784,13 +3784,13 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B125" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C125" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D125">
         <v>52</v>
@@ -3802,10 +3802,10 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C126" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D126">
         <v>57</v>
@@ -3817,13 +3817,13 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B127" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C127" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D127">
         <v>51</v>
@@ -3838,10 +3838,10 @@
         <v>12</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C128" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D128">
         <v>51</v>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C129" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D129">
         <v>51</v>
@@ -3871,7 +3871,7 @@
         <v>101</v>
       </c>
       <c r="C130" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D130">
         <v>57</v>
@@ -3886,7 +3886,7 @@
         <v>157</v>
       </c>
       <c r="C131" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D131">
         <v>54</v>
@@ -3901,7 +3901,7 @@
         <v>47</v>
       </c>
       <c r="C132" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D132">
         <v>57</v>
@@ -3913,13 +3913,13 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B133" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C133" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D133">
         <v>52</v>
@@ -3931,13 +3931,13 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B134" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C134" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D134">
         <v>54</v>
@@ -3949,13 +3949,13 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B135" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C135" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D135">
         <v>51</v>
@@ -3970,10 +3970,10 @@
         <v>33</v>
       </c>
       <c r="B136" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C136" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D136">
         <v>52</v>
@@ -3988,7 +3988,7 @@
         <v>135</v>
       </c>
       <c r="C137" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D137">
         <v>52</v>
@@ -4003,7 +4003,7 @@
         <v>178</v>
       </c>
       <c r="C138" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D138">
         <v>51</v>
@@ -4018,7 +4018,7 @@
         <v>109</v>
       </c>
       <c r="C139" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D139">
         <v>51</v>
@@ -4033,7 +4033,7 @@
         <v>142</v>
       </c>
       <c r="C140" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D140">
         <v>52</v>
@@ -4048,10 +4048,10 @@
         <v>26</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C141" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D141">
         <v>57</v>
@@ -4066,10 +4066,10 @@
         <v>18</v>
       </c>
       <c r="B142" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C142" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D142">
         <v>54</v>
@@ -4081,13 +4081,13 @@
     </row>
     <row r="143" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C143" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D143">
         <v>51</v>
@@ -4102,10 +4102,10 @@
         <v>25</v>
       </c>
       <c r="B144" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C144" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D144">
         <v>51</v>
@@ -4117,13 +4117,13 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B145" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C145" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D145">
         <v>51</v>
@@ -4135,13 +4135,13 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B146" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C146" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D146">
         <v>52</v>
@@ -4153,13 +4153,13 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B147" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C147" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D147">
         <v>52</v>
@@ -4174,7 +4174,7 @@
         <v>174</v>
       </c>
       <c r="C148" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D148">
         <v>52</v>
@@ -4186,10 +4186,10 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C149" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D149">
         <v>54</v>
@@ -4204,10 +4204,10 @@
         <v>65</v>
       </c>
       <c r="B150" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C150" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D150" s="3">
         <v>593</v>
@@ -4222,7 +4222,7 @@
         <v>4</v>
       </c>
       <c r="C151" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D151">
         <v>51</v>
@@ -4237,7 +4237,7 @@
         <v>118</v>
       </c>
       <c r="C152" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D152">
         <v>51</v>
@@ -4252,10 +4252,10 @@
         <v>172</v>
       </c>
       <c r="B153" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C153" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D153">
         <v>52</v>
@@ -4270,7 +4270,7 @@
         <v>177</v>
       </c>
       <c r="C154" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D154">
         <v>51</v>
@@ -4282,13 +4282,13 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B155" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C155" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D155">
         <v>52</v>
@@ -4303,7 +4303,7 @@
         <v>93</v>
       </c>
       <c r="C156" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D156">
         <v>51</v>
@@ -4318,10 +4318,10 @@
         <v>153</v>
       </c>
       <c r="B157" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C157" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D157">
         <v>58</v>
@@ -4336,10 +4336,10 @@
         <v>72</v>
       </c>
       <c r="B158" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C158" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D158">
         <v>51</v>
@@ -4354,7 +4354,7 @@
         <v>86</v>
       </c>
       <c r="C159" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D159">
         <v>51</v>
@@ -4369,7 +4369,7 @@
         <v>87</v>
       </c>
       <c r="C160" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D160">
         <v>51</v>
@@ -4384,7 +4384,7 @@
         <v>75</v>
       </c>
       <c r="C161" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D161">
         <v>51</v>
@@ -4396,10 +4396,10 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C162" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D162">
         <v>54</v>
@@ -4411,13 +4411,13 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B163" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C163" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D163">
         <v>51</v>
@@ -4429,13 +4429,13 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B164" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C164" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D164">
         <v>52</v>
@@ -4447,13 +4447,13 @@
     </row>
     <row r="165" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C165" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D165">
         <v>51</v>
@@ -4468,7 +4468,7 @@
         <v>78</v>
       </c>
       <c r="C166" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D166">
         <v>51</v>
@@ -4483,10 +4483,10 @@
         <v>147</v>
       </c>
       <c r="B167" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C167" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D167">
         <v>52</v>
@@ -4501,10 +4501,10 @@
         <v>59</v>
       </c>
       <c r="B168" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C168" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D168">
         <v>54</v>
@@ -4516,13 +4516,13 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B169" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C169" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D169">
         <v>52</v>
@@ -4534,10 +4534,10 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C170" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D170">
         <v>52</v>
@@ -4552,10 +4552,10 @@
         <v>35</v>
       </c>
       <c r="B171" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C171" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D171">
         <v>54</v>
@@ -4567,10 +4567,10 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C172" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D172">
         <v>52</v>
@@ -4582,13 +4582,13 @@
     </row>
     <row r="173" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C173" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D173">
         <v>51</v>
@@ -4603,7 +4603,7 @@
         <v>69</v>
       </c>
       <c r="C174" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D174">
         <v>506</v>
@@ -4615,10 +4615,10 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C175" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D175">
         <v>51</v>
@@ -4633,7 +4633,7 @@
         <v>167</v>
       </c>
       <c r="C176" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D176">
         <v>51</v>
@@ -4645,13 +4645,13 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B177" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C177" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D177">
         <v>53</v>
@@ -4666,7 +4666,7 @@
         <v>134</v>
       </c>
       <c r="C178" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D178">
         <v>52</v>
@@ -4681,7 +4681,7 @@
         <v>132</v>
       </c>
       <c r="C179" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D179">
         <v>52</v>
@@ -4696,10 +4696,10 @@
         <v>29</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C180" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D180">
         <v>51</v>
@@ -4714,10 +4714,10 @@
         <v>53</v>
       </c>
       <c r="B181" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C181" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D181">
         <v>52</v>
@@ -4732,10 +4732,10 @@
         <v>64</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C182" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D182">
         <v>51</v>
@@ -4753,7 +4753,7 @@
         <v>69865757</v>
       </c>
       <c r="C183" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D183">
         <v>591</v>
@@ -4768,10 +4768,10 @@
         <v>58</v>
       </c>
       <c r="B184" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C184" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D184">
         <v>506</v>
@@ -4786,7 +4786,7 @@
         <v>115</v>
       </c>
       <c r="C185" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D185">
         <v>58</v>
@@ -4798,13 +4798,13 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B186" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C186" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D186">
         <v>58</v>
@@ -4816,13 +4816,13 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B187">
         <v>6644057270</v>
       </c>
       <c r="C187" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D187">
         <v>52</v>
@@ -4837,10 +4837,10 @@
         <v>3</v>
       </c>
       <c r="B188" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C188" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D188">
         <v>51</v>
@@ -4855,7 +4855,7 @@
         <v>171</v>
       </c>
       <c r="C189" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D189">
         <v>51</v>
@@ -4870,7 +4870,7 @@
         <v>104</v>
       </c>
       <c r="C190" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D190">
         <v>52</v>
@@ -4885,10 +4885,10 @@
         <v>152</v>
       </c>
       <c r="B191" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C191" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D191">
         <v>52</v>
@@ -4903,7 +4903,7 @@
         <v>103</v>
       </c>
       <c r="C192" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D192">
         <v>51</v>
@@ -4915,10 +4915,10 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C193" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D193">
         <v>51</v>
@@ -4933,7 +4933,7 @@
         <v>80</v>
       </c>
       <c r="C194" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D194">
         <v>51</v>
@@ -4945,13 +4945,13 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B195" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C195" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D195">
         <v>52</v>
@@ -4963,10 +4963,10 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C196" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D196">
         <v>58</v>
@@ -4981,7 +4981,7 @@
         <v>173</v>
       </c>
       <c r="C197" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D197">
         <v>51</v>
@@ -4993,13 +4993,13 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B198" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C198" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D198">
         <v>52</v>
@@ -5014,10 +5014,10 @@
         <v>48</v>
       </c>
       <c r="B199" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C199" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D199">
         <v>52</v>
@@ -5029,10 +5029,10 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C200" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D200">
         <v>52</v>
@@ -5044,13 +5044,13 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B201" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C201" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D201">
         <v>52</v>
@@ -5065,7 +5065,7 @@
         <v>151</v>
       </c>
       <c r="C202" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D202">
         <v>56</v>
@@ -5077,10 +5077,10 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C203" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D203">
         <v>51</v>
@@ -5092,13 +5092,13 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B204" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C204" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D204">
         <v>53</v>
@@ -5113,7 +5113,7 @@
         <v>96</v>
       </c>
       <c r="C205" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D205">
         <v>51</v>
@@ -5125,13 +5125,13 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B206" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C206" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D206">
         <v>58</v>
@@ -5146,7 +5146,7 @@
         <v>97</v>
       </c>
       <c r="C207" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D207">
         <v>51</v>
@@ -5161,10 +5161,10 @@
         <v>28</v>
       </c>
       <c r="B208" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C208" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D208">
         <v>51</v>
@@ -5176,10 +5176,10 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C209" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D209">
         <v>51</v>
@@ -5194,10 +5194,10 @@
         <v>145</v>
       </c>
       <c r="B210" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C210" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D210">
         <v>56</v>
@@ -5212,10 +5212,10 @@
         <v>7</v>
       </c>
       <c r="B211" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C211" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D211">
         <v>51</v>
@@ -5230,10 +5230,10 @@
         <v>15</v>
       </c>
       <c r="B212" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C212" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D212">
         <v>51</v>
@@ -5245,10 +5245,10 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C213" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D213">
         <v>51</v>
@@ -5263,10 +5263,10 @@
         <v>40</v>
       </c>
       <c r="B214" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C214" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D214">
         <v>58</v>
@@ -5281,7 +5281,7 @@
         <v>91</v>
       </c>
       <c r="C215" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D215">
         <v>51</v>
@@ -5293,13 +5293,13 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B216" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C216" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D216">
         <v>52</v>
@@ -5314,10 +5314,10 @@
         <v>14</v>
       </c>
       <c r="B217" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C217" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D217">
         <v>506</v>
@@ -5332,7 +5332,7 @@
         <v>67</v>
       </c>
       <c r="C218" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D218">
         <v>503</v>
@@ -5347,7 +5347,7 @@
         <v>116</v>
       </c>
       <c r="C219" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D219">
         <v>54</v>
@@ -5362,10 +5362,10 @@
         <v>164</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C220" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D220">
         <v>51</v>
@@ -5380,10 +5380,10 @@
         <v>148</v>
       </c>
       <c r="B221" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C221" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D221">
         <v>58</v>
@@ -5398,7 +5398,7 @@
         <v>98</v>
       </c>
       <c r="C222" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D222">
         <v>54</v>
@@ -5410,10 +5410,10 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C223" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D223">
         <v>51</v>
@@ -5428,7 +5428,7 @@
         <v>79</v>
       </c>
       <c r="C224" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D224">
         <v>51</v>
@@ -5443,10 +5443,10 @@
         <v>60</v>
       </c>
       <c r="B225" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C225" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D225">
         <v>58</v>
@@ -5461,10 +5461,10 @@
         <v>158</v>
       </c>
       <c r="B226" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C226" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D226">
         <v>1</v>
@@ -5476,13 +5476,13 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B227" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C227" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D227">
         <v>52</v>
@@ -5497,7 +5497,7 @@
         <v>6</v>
       </c>
       <c r="C228" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D228">
         <v>51</v>
@@ -5512,7 +5512,7 @@
         <v>36</v>
       </c>
       <c r="C229" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D229">
         <v>51</v>
@@ -5527,7 +5527,7 @@
         <v>123</v>
       </c>
       <c r="C230" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D230">
         <v>54</v>
@@ -5542,7 +5542,7 @@
         <v>73</v>
       </c>
       <c r="C231" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D231">
         <v>51</v>
@@ -5557,7 +5557,7 @@
         <v>85</v>
       </c>
       <c r="C232" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D232">
         <v>51</v>
@@ -5569,10 +5569,10 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C233" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D233">
         <v>54</v>
@@ -5587,7 +5587,7 @@
         <v>143</v>
       </c>
       <c r="C234" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D234">
         <v>54</v>
@@ -5599,10 +5599,10 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C235" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D235">
         <v>52</v>
@@ -5614,13 +5614,13 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B236" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C236" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D236">
         <v>51</v>
@@ -5635,7 +5635,7 @@
         <v>81</v>
       </c>
       <c r="C237" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D237">
         <v>51</v>
@@ -5650,10 +5650,10 @@
         <v>19</v>
       </c>
       <c r="B238" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C238" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D238">
         <v>51</v>
@@ -5671,7 +5671,7 @@
         <v>972691544</v>
       </c>
       <c r="C239" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D239">
         <v>51</v>
@@ -5683,13 +5683,13 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B240" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C240" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D240">
         <v>53</v>
@@ -5701,10 +5701,10 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C241" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D241">
         <v>52</v>
@@ -5716,10 +5716,10 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C242" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D242">
         <v>54</v>
@@ -5734,7 +5734,7 @@
         <v>131</v>
       </c>
       <c r="C243" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D243">
         <v>51</v>
@@ -5746,10 +5746,10 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C244" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D244">
         <v>54</v>
@@ -5764,7 +5764,7 @@
         <v>76</v>
       </c>
       <c r="C245" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D245">
         <v>51</v>
@@ -5779,7 +5779,7 @@
         <v>49</v>
       </c>
       <c r="C246" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D246">
         <v>51</v>
@@ -5794,10 +5794,10 @@
         <v>24</v>
       </c>
       <c r="B247" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C247" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D247">
         <v>51</v>
@@ -5812,10 +5812,10 @@
         <v>102</v>
       </c>
       <c r="B248" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C248" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D248">
         <v>51</v>
@@ -5830,10 +5830,10 @@
         <v>170</v>
       </c>
       <c r="B249" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C249" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D249">
         <v>51</v>
@@ -5845,10 +5845,10 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C250" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D250">
         <v>51</v>
@@ -5863,7 +5863,7 @@
         <v>82</v>
       </c>
       <c r="C251" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D251">
         <v>51</v>
@@ -5878,10 +5878,10 @@
         <v>1</v>
       </c>
       <c r="B252" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C252" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D252">
         <v>51</v>
@@ -5893,10 +5893,10 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C253" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D253">
         <v>52</v>
@@ -5911,10 +5911,10 @@
         <v>63</v>
       </c>
       <c r="B254" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C254" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D254">
         <v>51</v>
@@ -5926,13 +5926,13 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B255" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C255" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D255">
         <v>52</v>
@@ -5944,13 +5944,13 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B256" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C256" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D256">
         <v>52</v>
@@ -5962,10 +5962,10 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C257" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D257">
         <v>58</v>
@@ -5980,10 +5980,10 @@
         <v>70</v>
       </c>
       <c r="B258" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C258" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D258">
         <v>51</v>
@@ -5998,7 +5998,7 @@
         <v>144</v>
       </c>
       <c r="C259" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D259">
         <v>52</v>
@@ -6013,7 +6013,7 @@
         <v>95</v>
       </c>
       <c r="C260" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D260">
         <v>52</v>
@@ -6028,10 +6028,10 @@
         <v>62</v>
       </c>
       <c r="B261" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C261" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D261">
         <v>54</v>
@@ -6046,10 +6046,10 @@
         <v>11</v>
       </c>
       <c r="B262" t="s">
+        <v>357</v>
+      </c>
+      <c r="C262" t="s">
         <v>358</v>
-      </c>
-      <c r="C262" t="s">
-        <v>359</v>
       </c>
       <c r="D262">
         <v>502</v>
@@ -6061,13 +6061,13 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
+        <v>403</v>
+      </c>
+      <c r="B263" t="s">
         <v>404</v>
       </c>
-      <c r="B263" t="s">
-        <v>405</v>
-      </c>
       <c r="C263" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D263">
         <v>57</v>
@@ -6079,13 +6079,13 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
+        <v>405</v>
+      </c>
+      <c r="B264" t="s">
         <v>406</v>
       </c>
-      <c r="B264" t="s">
-        <v>407</v>
-      </c>
       <c r="C264" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D264">
         <v>54</v>
@@ -6097,10 +6097,10 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C265" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D265">
         <v>51</v>
@@ -6112,13 +6112,13 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
+        <v>409</v>
+      </c>
+      <c r="B266" t="s">
         <v>410</v>
       </c>
-      <c r="B266" t="s">
-        <v>411</v>
-      </c>
       <c r="C266" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D266">
         <v>51</v>
@@ -6130,13 +6130,13 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
+        <v>415</v>
+      </c>
+      <c r="B267" t="s">
         <v>416</v>
       </c>
-      <c r="B267" t="s">
-        <v>417</v>
-      </c>
       <c r="C267" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D267">
         <v>58</v>
@@ -6148,13 +6148,13 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
+        <v>417</v>
+      </c>
+      <c r="B268" t="s">
         <v>418</v>
       </c>
-      <c r="B268" t="s">
-        <v>419</v>
-      </c>
       <c r="C268" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D268">
         <v>503</v>
@@ -6166,13 +6166,13 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C269" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D269">
         <v>51</v>

--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DF062A-B395-410E-981E-0477E725E9DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A88D247-892F-46C0-BD95-3B280B3E9D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
@@ -1269,9 +1269,6 @@
     <t>mathixd1</t>
   </si>
   <si>
-    <t xml:space="preserve"> 966 803 562</t>
-  </si>
-  <si>
     <t>849 763-2529</t>
   </si>
   <si>
@@ -1318,6 +1315,9 @@
   </si>
   <si>
     <t>Caua</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 982 638 611</t>
   </si>
 </sst>
 </file>
@@ -2299,7 +2299,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B36" t="s">
         <v>295</v>
@@ -2872,7 +2872,7 @@
         <v>159</v>
       </c>
       <c r="B70" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C70" t="s">
         <v>277</v>
@@ -2890,7 +2890,7 @@
         <v>74</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C71" t="s">
         <v>269</v>
@@ -2908,7 +2908,7 @@
         <v>193</v>
       </c>
       <c r="B72" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C72" t="s">
         <v>266</v>
@@ -3415,7 +3415,7 @@
         <v>55</v>
       </c>
       <c r="B103" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C103" t="s">
         <v>277</v>
@@ -3685,7 +3685,7 @@
         <v>165</v>
       </c>
       <c r="B119" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C119" t="s">
         <v>277</v>
@@ -4120,7 +4120,7 @@
         <v>243</v>
       </c>
       <c r="B145" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C145" t="s">
         <v>269</v>
@@ -5362,7 +5362,7 @@
         <v>164</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C220" t="s">
         <v>269</v>
@@ -5461,7 +5461,7 @@
         <v>158</v>
       </c>
       <c r="B226" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C226" t="s">
         <v>356</v>
@@ -5830,7 +5830,7 @@
         <v>170</v>
       </c>
       <c r="B249" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C249" t="s">
         <v>269</v>
@@ -6115,7 +6115,7 @@
         <v>409</v>
       </c>
       <c r="B266" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="C266" t="s">
         <v>269</v>
@@ -6125,15 +6125,15 @@
       </c>
       <c r="E266" t="str">
         <f t="shared" ref="E266" si="6">CONCATENATE("+",D266," ",B266)</f>
-        <v>+51  966 803 562</v>
+        <v>+51  982 638 611</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
+        <v>414</v>
+      </c>
+      <c r="B267" t="s">
         <v>415</v>
-      </c>
-      <c r="B267" t="s">
-        <v>416</v>
       </c>
       <c r="C267" t="s">
         <v>268</v>
@@ -6148,10 +6148,10 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
+        <v>416</v>
+      </c>
+      <c r="B268" t="s">
         <v>417</v>
-      </c>
-      <c r="B268" t="s">
-        <v>418</v>
       </c>
       <c r="C268" t="s">
         <v>380</v>
@@ -6166,10 +6166,10 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C269" t="s">
         <v>269</v>

--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A88D247-892F-46C0-BD95-3B280B3E9D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BC758B-F85C-4330-8E68-C383A3BB7EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
@@ -498,9 +498,6 @@
     <t>Pawerrr</t>
   </si>
   <si>
-    <t>masafesio</t>
-  </si>
-  <si>
     <t>HallacAs</t>
   </si>
   <si>
@@ -1318,6 +1315,9 @@
   </si>
   <si>
     <t xml:space="preserve"> 982 638 611</t>
+  </si>
+  <si>
+    <t>darkam580</t>
   </si>
 </sst>
 </file>
@@ -1693,6 +1693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E269"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1703,27 +1704,27 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B1" t="s">
         <v>259</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>260</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E1" t="s">
         <v>261</v>
       </c>
-      <c r="D1" t="s">
-        <v>263</v>
-      </c>
-      <c r="E1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D2">
         <v>51</v>
@@ -1733,15 +1734,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D3">
         <v>51</v>
@@ -1751,15 +1752,15 @@
         <v>+51 933 668 277</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D4">
         <v>51</v>
@@ -1769,15 +1770,15 @@
         <v>+51 980 596 555</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>38</v>
       </c>
       <c r="B5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D5">
         <v>58</v>
@@ -1787,12 +1788,12 @@
         <v>+58 424-7086947</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D6">
         <v>51</v>
@@ -1802,15 +1803,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D7">
         <v>58</v>
@@ -1820,15 +1821,15 @@
         <v>+58 412-1322018</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B8" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D8">
         <v>56</v>
@@ -1838,12 +1839,12 @@
         <v>+56 9 7927 3083</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D9">
         <v>52</v>
@@ -1853,15 +1854,15 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D10">
         <v>51</v>
@@ -1871,15 +1872,15 @@
         <v>+51 985 699 608</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D11">
         <v>52</v>
@@ -1889,15 +1890,15 @@
         <v>+52 1 56 1007 9583</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B12" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D12">
         <v>52</v>
@@ -1907,12 +1908,12 @@
         <v>+52 1 81 2944 2313</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D13">
         <v>51</v>
@@ -1922,12 +1923,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D14">
         <v>51</v>
@@ -1937,12 +1938,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D15">
         <v>51</v>
@@ -1952,15 +1953,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C16" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D16">
         <v>51</v>
@@ -1970,12 +1971,12 @@
         <v>+51  984 190 584</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>149</v>
       </c>
       <c r="C17" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D17">
         <v>57</v>
@@ -1985,15 +1986,15 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C18" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D18">
         <v>51</v>
@@ -2003,15 +2004,15 @@
         <v>+51 984 267 160</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C19" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D19">
         <v>51</v>
@@ -2021,12 +2022,12 @@
         <v>+51  912 858 811</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>127</v>
       </c>
       <c r="C20" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D20">
         <v>51</v>
@@ -2036,15 +2037,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>136</v>
       </c>
       <c r="B21" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C21" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D21">
         <v>51</v>
@@ -2054,15 +2055,15 @@
         <v>+51 949 647 819</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C22" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D22">
         <v>34</v>
@@ -2072,12 +2073,12 @@
         <v>+34  646 20 50 99</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D23">
         <v>51</v>
@@ -2087,15 +2088,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>137</v>
       </c>
       <c r="B24" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C24" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D24">
         <v>52</v>
@@ -2105,15 +2106,15 @@
         <v>+52  1 222 102 8165</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C25" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D25">
         <v>58</v>
@@ -2123,7 +2124,7 @@
         <v>+58 416-4398466</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>129</v>
       </c>
@@ -2131,7 +2132,7 @@
         <v>91139028131</v>
       </c>
       <c r="C26" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D26">
         <v>54</v>
@@ -2141,15 +2142,15 @@
         <v>+54 91139028131</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>138</v>
       </c>
       <c r="B27" t="s">
+        <v>290</v>
+      </c>
+      <c r="C27" t="s">
         <v>291</v>
-      </c>
-      <c r="C27" t="s">
-        <v>292</v>
       </c>
       <c r="D27">
         <v>57</v>
@@ -2159,15 +2160,15 @@
         <v>+57 322 4761144</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C28" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D28">
         <v>52</v>
@@ -2177,15 +2178,15 @@
         <v>+52 1 771 306 4084</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B29" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C29" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D29">
         <v>58</v>
@@ -2195,7 +2196,7 @@
         <v>+58 412-7060529</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -2203,7 +2204,7 @@
         <v>933448842</v>
       </c>
       <c r="C30" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D30">
         <v>51</v>
@@ -2213,12 +2214,12 @@
         <v>+51 933448842</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>37</v>
       </c>
       <c r="C31" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D31">
         <v>51</v>
@@ -2228,7 +2229,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -2236,7 +2237,7 @@
         <v>912358537</v>
       </c>
       <c r="C32" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D32">
         <v>51</v>
@@ -2246,15 +2247,15 @@
         <v>+51 912358537</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B33" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C33" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D33">
         <v>51</v>
@@ -2264,15 +2265,15 @@
         <v>+51 950 746 501</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C34" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D34">
         <v>54</v>
@@ -2282,12 +2283,12 @@
         <v>+54 9 3794 73 7373</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>119</v>
       </c>
       <c r="C35" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D35">
         <v>52</v>
@@ -2297,15 +2298,15 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B36" t="s">
+        <v>294</v>
+      </c>
+      <c r="C36" t="s">
         <v>295</v>
-      </c>
-      <c r="C36" t="s">
-        <v>296</v>
       </c>
       <c r="D36">
         <v>55</v>
@@ -2315,15 +2316,15 @@
         <v>+55 71 9370-7438</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C37" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D37">
         <v>51</v>
@@ -2333,15 +2334,15 @@
         <v>+51 991 176 689</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>121</v>
       </c>
       <c r="B38" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C38" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D38">
         <v>34</v>
@@ -2351,12 +2352,12 @@
         <v>+34 601 36 84 69</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>71</v>
       </c>
       <c r="C39" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D39">
         <v>51</v>
@@ -2366,15 +2367,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B40" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C40" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D40">
         <v>51</v>
@@ -2384,15 +2385,15 @@
         <v>+51  917 057 695</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C41" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D41">
         <v>34</v>
@@ -2402,12 +2403,12 @@
         <v>+34 608 39 51 22</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C42" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D42">
         <v>51</v>
@@ -2417,12 +2418,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>117</v>
       </c>
       <c r="C43" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D43">
         <v>51</v>
@@ -2432,12 +2433,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>99</v>
       </c>
       <c r="C44" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D44">
         <v>51</v>
@@ -2447,15 +2448,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B45">
         <v>93854880470</v>
       </c>
       <c r="C45" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D45">
         <v>54</v>
@@ -2465,7 +2466,7 @@
         <v>+54 93854880470</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>61</v>
       </c>
@@ -2473,7 +2474,7 @@
         <v>51162846</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D46">
         <v>53</v>
@@ -2483,12 +2484,12 @@
         <v>+53 51162846</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C47" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -2498,12 +2499,12 @@
         <v xml:space="preserve">+1 </v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>57</v>
       </c>
       <c r="C48" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D48">
         <v>58</v>
@@ -2513,15 +2514,15 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>10</v>
       </c>
       <c r="B49" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C49" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D49">
         <v>51</v>
@@ -2531,15 +2532,15 @@
         <v>+51  920 449 371</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>68</v>
       </c>
       <c r="B50" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C50" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D50">
         <v>51</v>
@@ -2549,12 +2550,12 @@
         <v>+51  912 209 142</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>105</v>
       </c>
       <c r="C51" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D51">
         <v>51</v>
@@ -2564,15 +2565,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>0</v>
       </c>
       <c r="B52" t="s">
+        <v>302</v>
+      </c>
+      <c r="C52" t="s">
         <v>303</v>
-      </c>
-      <c r="C52" t="s">
-        <v>304</v>
       </c>
       <c r="D52">
         <v>505</v>
@@ -2582,15 +2583,15 @@
         <v>+505 8799 9543</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>125</v>
       </c>
       <c r="B53" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C53" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -2600,15 +2601,15 @@
         <v>+52 1 686 589 5829</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B54" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C54" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D54">
         <v>51</v>
@@ -2618,12 +2619,12 @@
         <v>+51 992 067 030</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>108</v>
       </c>
       <c r="C55" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D55">
         <v>57</v>
@@ -2633,12 +2634,12 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
       <c r="C56" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D56">
         <v>51</v>
@@ -2648,12 +2649,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C57" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D57">
         <v>58</v>
@@ -2663,15 +2664,15 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>32</v>
       </c>
       <c r="B58" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C58" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D58">
         <v>58</v>
@@ -2681,15 +2682,15 @@
         <v>+58  412-7396859</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>111</v>
       </c>
       <c r="B59" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C59" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D59">
         <v>52</v>
@@ -2699,12 +2700,12 @@
         <v>+52 1 921 208 0809</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>100</v>
       </c>
       <c r="C60" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D60">
         <v>51</v>
@@ -2714,15 +2715,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B61" t="s">
+        <v>373</v>
+      </c>
+      <c r="C61" t="s">
         <v>374</v>
-      </c>
-      <c r="C61" t="s">
-        <v>375</v>
       </c>
       <c r="D61">
         <v>504</v>
@@ -2732,7 +2733,7 @@
         <v>+504 3204-1711</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>128</v>
       </c>
@@ -2740,7 +2741,7 @@
         <v>99797773</v>
       </c>
       <c r="C62" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D62">
         <v>56</v>
@@ -2750,12 +2751,12 @@
         <v>+56 99797773</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C63" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D63">
         <v>51</v>
@@ -2765,15 +2766,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>39</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>277</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -2783,15 +2784,15 @@
         <v>+1 305 8902347</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B65" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C65" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D65">
         <v>52</v>
@@ -2801,12 +2802,12 @@
         <v>+52 1 861 128 3193</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>124</v>
       </c>
       <c r="C66" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D66">
         <v>58</v>
@@ -2816,12 +2817,12 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C67" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D67">
         <v>58</v>
@@ -2831,15 +2832,15 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B68">
         <v>8341048014</v>
       </c>
       <c r="C68" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D68">
         <v>52</v>
@@ -2849,15 +2850,15 @@
         <v>+52 8341048014</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>5</v>
       </c>
       <c r="B69" t="s">
+        <v>308</v>
+      </c>
+      <c r="C69" t="s">
         <v>309</v>
-      </c>
-      <c r="C69" t="s">
-        <v>310</v>
       </c>
       <c r="D69">
         <v>506</v>
@@ -2867,15 +2868,15 @@
         <v>+506  8936 2350</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B70" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C70" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -2885,15 +2886,15 @@
         <v>+1 253 212-8032</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>74</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C71" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D71">
         <v>51</v>
@@ -2903,15 +2904,15 @@
         <v>+51 991 846 357</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B72" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C72" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D72">
         <v>52</v>
@@ -2921,12 +2922,12 @@
         <v>+52 1 33 4442 1918</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>110</v>
       </c>
       <c r="C73" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D73">
         <v>51</v>
@@ -2936,12 +2937,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C74" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D74">
         <v>57</v>
@@ -2951,12 +2952,12 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C75" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D75">
         <v>54</v>
@@ -2966,15 +2967,15 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>31</v>
       </c>
       <c r="B76" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C76" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D76">
         <v>51</v>
@@ -2984,12 +2985,12 @@
         <v>+51  912 058 374</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>88</v>
       </c>
       <c r="C77" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D77">
         <v>51</v>
@@ -2999,12 +3000,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>133</v>
       </c>
       <c r="C78" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D78">
         <v>58</v>
@@ -3014,12 +3015,12 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>90</v>
       </c>
       <c r="C79" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D79">
         <v>51</v>
@@ -3029,12 +3030,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>106</v>
       </c>
       <c r="C80" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D80">
         <v>52</v>
@@ -3044,15 +3045,15 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B81" t="s">
+        <v>311</v>
+      </c>
+      <c r="C81" t="s">
         <v>312</v>
-      </c>
-      <c r="C81" t="s">
-        <v>313</v>
       </c>
       <c r="D81">
         <v>593</v>
@@ -3062,12 +3063,12 @@
         <v>+593  96 083 0485</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>112</v>
       </c>
       <c r="C82" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D82">
         <v>505</v>
@@ -3077,12 +3078,12 @@
         <v xml:space="preserve">+505 </v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>107</v>
       </c>
       <c r="C83" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D83">
         <v>52</v>
@@ -3092,15 +3093,15 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>44</v>
       </c>
       <c r="B84" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C84" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D84">
         <v>51</v>
@@ -3110,12 +3111,12 @@
         <v>+51  983 379 394</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>66</v>
       </c>
       <c r="C85" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D85">
         <v>54</v>
@@ -3125,15 +3126,15 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B86" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C86" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D86">
         <v>51</v>
@@ -3143,12 +3144,12 @@
         <v>+51 980 679 898</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C87" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D87">
         <v>54</v>
@@ -3158,15 +3159,15 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>139</v>
       </c>
       <c r="B88" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C88" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D88">
         <v>53</v>
@@ -3176,15 +3177,15 @@
         <v>+53  5 6467775</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B89">
         <v>943126988</v>
       </c>
       <c r="C89" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D89">
         <v>51</v>
@@ -3194,12 +3195,12 @@
         <v>+51 943126988</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>122</v>
       </c>
       <c r="C90" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D90">
         <v>593</v>
@@ -3209,12 +3210,12 @@
         <v xml:space="preserve">+593 </v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C91" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D91">
         <v>52</v>
@@ -3224,15 +3225,15 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>45</v>
       </c>
       <c r="B92" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C92" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D92">
         <v>54</v>
@@ -3242,12 +3243,12 @@
         <v>+54 9 3412 81-3587</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>89</v>
       </c>
       <c r="C93" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D93">
         <v>51</v>
@@ -3257,15 +3258,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>120</v>
       </c>
       <c r="B94" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C94" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D94">
         <v>57</v>
@@ -3275,15 +3276,15 @@
         <v>+57  302 5578252</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B95" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C95" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D95">
         <v>593</v>
@@ -3293,15 +3294,15 @@
         <v>+593 96 151 5565</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B96" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C96" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D96">
         <v>51</v>
@@ -3311,15 +3312,15 @@
         <v>+51 956 677 392</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B97" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C97" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D97">
         <v>54</v>
@@ -3329,15 +3330,15 @@
         <v>+54 9 11 2783 9968</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B98" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C98" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D98">
         <v>51</v>
@@ -3347,15 +3348,15 @@
         <v>+51 961 492 733</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>34</v>
       </c>
       <c r="B99" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C99" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D99">
         <v>53</v>
@@ -3365,12 +3366,12 @@
         <v>+53 5 1113536</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>140</v>
       </c>
       <c r="C100" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D100">
         <v>54</v>
@@ -3380,12 +3381,12 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C101" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D101">
         <v>54</v>
@@ -3395,12 +3396,12 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>141</v>
       </c>
       <c r="C102" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D102">
         <v>57</v>
@@ -3410,15 +3411,15 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>55</v>
       </c>
       <c r="B103" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C103" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -3428,15 +3429,15 @@
         <v>+1 809 658-5500</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B104" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C104" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D104">
         <v>58</v>
@@ -3446,15 +3447,15 @@
         <v>+58 424-1216695</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B105" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C105" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D105">
         <v>51</v>
@@ -3464,15 +3465,15 @@
         <v>+51 963 745 855</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B106" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C106" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D106">
         <v>51</v>
@@ -3482,15 +3483,15 @@
         <v>+51  960 274 071</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>114</v>
       </c>
       <c r="B107" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C107" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D107">
         <v>593</v>
@@ -3500,12 +3501,12 @@
         <v>+593 98 768 2900</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>94</v>
       </c>
       <c r="C108" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D108">
         <v>52</v>
@@ -3515,15 +3516,15 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B109" t="s">
+        <v>378</v>
+      </c>
+      <c r="C109" t="s">
         <v>379</v>
-      </c>
-      <c r="C109" t="s">
-        <v>380</v>
       </c>
       <c r="D109">
         <v>503</v>
@@ -3533,12 +3534,12 @@
         <v>+503 7868 0662</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C110" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D110">
         <v>51</v>
@@ -3548,15 +3549,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B111" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C111" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D111">
         <v>58</v>
@@ -3566,7 +3567,7 @@
         <v>+58 414-4473628</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>43</v>
       </c>
@@ -3574,7 +3575,7 @@
         <v>3054850698</v>
       </c>
       <c r="C112" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D112">
         <v>57</v>
@@ -3584,12 +3585,12 @@
         <v>+57 3054850698</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C113" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D113">
         <v>51</v>
@@ -3599,12 +3600,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C114" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D114">
         <v>51</v>
@@ -3614,12 +3615,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>56</v>
       </c>
       <c r="C115" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D115">
         <v>507</v>
@@ -3629,15 +3630,15 @@
         <v xml:space="preserve">+507 </v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>150</v>
       </c>
       <c r="B116" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C116" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D116">
         <v>58</v>
@@ -3647,15 +3648,15 @@
         <v>+58  412-1885430</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>130</v>
       </c>
       <c r="B117" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C117" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D117">
         <v>51</v>
@@ -3665,12 +3666,12 @@
         <v>+51  906 691 465</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>146</v>
       </c>
       <c r="C118" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D118">
         <v>51</v>
@@ -3680,15 +3681,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B119" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C119" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -3698,15 +3699,15 @@
         <v>+1  787 513-4231</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>46</v>
       </c>
       <c r="B120" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C120" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D120">
         <v>507</v>
@@ -3716,15 +3717,15 @@
         <v>+507  6898-7574</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B121" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C121" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D121">
         <v>52</v>
@@ -3734,12 +3735,12 @@
         <v>+52 1 444 674 9780</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>2</v>
       </c>
       <c r="C122" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D122">
         <v>51</v>
@@ -3749,15 +3750,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>21</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C123" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D123">
         <v>51</v>
@@ -3767,12 +3768,12 @@
         <v>+51 996 668 615</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>77</v>
       </c>
       <c r="C124" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D124">
         <v>51</v>
@@ -3782,15 +3783,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B125" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C125" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D125">
         <v>52</v>
@@ -3800,12 +3801,12 @@
         <v>+52 1 55 3845 6274</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C126" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D126">
         <v>57</v>
@@ -3815,15 +3816,15 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B127" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C127" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D127">
         <v>51</v>
@@ -3833,15 +3834,15 @@
         <v>+51  921 447 908</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>12</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C128" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D128">
         <v>51</v>
@@ -3851,12 +3852,12 @@
         <v>+51 976 413 331</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C129" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D129">
         <v>51</v>
@@ -3866,12 +3867,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>101</v>
       </c>
       <c r="C130" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D130">
         <v>57</v>
@@ -3881,12 +3882,12 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C131" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D131">
         <v>54</v>
@@ -3896,12 +3897,12 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>47</v>
       </c>
       <c r="C132" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D132">
         <v>57</v>
@@ -3911,15 +3912,15 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B133" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C133" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D133">
         <v>52</v>
@@ -3929,15 +3930,15 @@
         <v>+52 Juni Frostheart</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B134" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C134" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D134">
         <v>54</v>
@@ -3947,15 +3948,15 @@
         <v>+54 9 11 2526 8333</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B135" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C135" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D135">
         <v>51</v>
@@ -3965,15 +3966,15 @@
         <v>+51 963 347 387</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>33</v>
       </c>
       <c r="B136" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C136" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D136">
         <v>52</v>
@@ -3983,12 +3984,12 @@
         <v>+52 1 81 2684 3183</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>135</v>
       </c>
       <c r="C137" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D137">
         <v>52</v>
@@ -3998,12 +3999,12 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C138" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D138">
         <v>51</v>
@@ -4013,12 +4014,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>109</v>
       </c>
       <c r="C139" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D139">
         <v>51</v>
@@ -4028,12 +4029,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>142</v>
       </c>
       <c r="C140" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D140">
         <v>52</v>
@@ -4043,15 +4044,15 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>26</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C141" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D141">
         <v>57</v>
@@ -4061,15 +4062,15 @@
         <v>+57 302 3773516</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>18</v>
       </c>
       <c r="B142" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C142" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D142">
         <v>54</v>
@@ -4079,15 +4080,15 @@
         <v>+54  9 11 2372-2211</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C143" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D143">
         <v>51</v>
@@ -4097,15 +4098,15 @@
         <v>+51 960 749 072</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>25</v>
       </c>
       <c r="B144" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C144" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D144">
         <v>51</v>
@@ -4115,15 +4116,15 @@
         <v>+51 984 784 816</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B145" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C145" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D145">
         <v>51</v>
@@ -4133,15 +4134,15 @@
         <v>+51 986 579 683</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B146" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C146" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D146">
         <v>52</v>
@@ -4151,15 +4152,15 @@
         <v>+52 1 614 529 6392</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B147" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C147" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D147">
         <v>52</v>
@@ -4169,12 +4170,12 @@
         <v>+52 1 287 154 7879</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C148" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D148">
         <v>52</v>
@@ -4184,12 +4185,12 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C149" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D149">
         <v>54</v>
@@ -4199,15 +4200,15 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>65</v>
       </c>
       <c r="B150" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C150" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D150" s="3">
         <v>593</v>
@@ -4217,12 +4218,12 @@
         <v>+593 98 174 5020</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>4</v>
       </c>
       <c r="C151" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D151">
         <v>51</v>
@@ -4232,12 +4233,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>118</v>
       </c>
       <c r="C152" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D152">
         <v>51</v>
@@ -4247,15 +4248,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B153" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C153" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D153">
         <v>52</v>
@@ -4265,12 +4266,12 @@
         <v>+52 1 771 297 6010</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C154" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D154">
         <v>51</v>
@@ -4280,15 +4281,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B155" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C155" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D155">
         <v>52</v>
@@ -4298,12 +4299,12 @@
         <v>+52  1 983 752 2450</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>93</v>
       </c>
       <c r="C156" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D156">
         <v>51</v>
@@ -4315,13 +4316,13 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>153</v>
+        <v>426</v>
       </c>
       <c r="B157" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C157" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D157">
         <v>58</v>
@@ -4331,15 +4332,15 @@
         <v>+58 424-6956750</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>72</v>
       </c>
       <c r="B158" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C158" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D158">
         <v>51</v>
@@ -4349,12 +4350,12 @@
         <v>+51  965 337 810</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>86</v>
       </c>
       <c r="C159" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D159">
         <v>51</v>
@@ -4364,12 +4365,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>87</v>
       </c>
       <c r="C160" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D160">
         <v>51</v>
@@ -4379,12 +4380,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>75</v>
       </c>
       <c r="C161" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D161">
         <v>51</v>
@@ -4394,12 +4395,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C162" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D162">
         <v>54</v>
@@ -4409,15 +4410,15 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B163" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C163" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D163">
         <v>51</v>
@@ -4427,15 +4428,15 @@
         <v>+51  945 349 568</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B164" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C164" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D164">
         <v>52</v>
@@ -4445,15 +4446,15 @@
         <v>+52 1 735 162 2046</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C165" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D165">
         <v>51</v>
@@ -4463,12 +4464,12 @@
         <v>+51 970 857 085</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>78</v>
       </c>
       <c r="C166" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D166">
         <v>51</v>
@@ -4478,15 +4479,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>147</v>
       </c>
       <c r="B167" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C167" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D167">
         <v>52</v>
@@ -4496,15 +4497,15 @@
         <v>+52  1 673 472 3074</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>59</v>
       </c>
       <c r="B168" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C168" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D168">
         <v>54</v>
@@ -4514,15 +4515,15 @@
         <v>+54 9 2974 22-6785</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B169" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C169" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D169">
         <v>52</v>
@@ -4532,12 +4533,12 @@
         <v>+52 1 55 1805 8456</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C170" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D170">
         <v>52</v>
@@ -4547,15 +4548,15 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>35</v>
       </c>
       <c r="B171" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C171" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D171">
         <v>54</v>
@@ -4565,12 +4566,12 @@
         <v>+54  9 11 6135-9811</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C172" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D172">
         <v>52</v>
@@ -4580,15 +4581,15 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C173" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D173">
         <v>51</v>
@@ -4598,12 +4599,12 @@
         <v>+51 991 342 085</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>69</v>
       </c>
       <c r="C174" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D174">
         <v>506</v>
@@ -4613,12 +4614,12 @@
         <v xml:space="preserve">+506 </v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C175" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D175">
         <v>51</v>
@@ -4628,12 +4629,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C176" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D176">
         <v>51</v>
@@ -4643,15 +4644,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B177" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C177" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D177">
         <v>53</v>
@@ -4661,12 +4662,12 @@
         <v>+53 5 6957902</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>134</v>
       </c>
       <c r="C178" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D178">
         <v>52</v>
@@ -4676,12 +4677,12 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>132</v>
       </c>
       <c r="C179" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D179">
         <v>52</v>
@@ -4691,15 +4692,15 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>29</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C180" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D180">
         <v>51</v>
@@ -4709,15 +4710,15 @@
         <v>+51 977 404 957</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>53</v>
       </c>
       <c r="B181" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C181" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D181">
         <v>52</v>
@@ -4727,15 +4728,15 @@
         <v>+52 1 229 229 9515</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>64</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C182" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D182">
         <v>51</v>
@@ -4745,7 +4746,7 @@
         <v>+51 986 824 543</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>16</v>
       </c>
@@ -4753,7 +4754,7 @@
         <v>69865757</v>
       </c>
       <c r="C183" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D183">
         <v>591</v>
@@ -4763,15 +4764,15 @@
         <v>+591 69865757</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>58</v>
       </c>
       <c r="B184" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C184" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D184">
         <v>506</v>
@@ -4781,12 +4782,12 @@
         <v>+506  7139 5493</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>115</v>
       </c>
       <c r="C185" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D185">
         <v>58</v>
@@ -4796,15 +4797,15 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B186" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C186" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D186">
         <v>58</v>
@@ -4814,15 +4815,15 @@
         <v>+58 424-2233503</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B187">
         <v>6644057270</v>
       </c>
       <c r="C187" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D187">
         <v>52</v>
@@ -4832,15 +4833,15 @@
         <v>+52 6644057270</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>3</v>
       </c>
       <c r="B188" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C188" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D188">
         <v>51</v>
@@ -4850,12 +4851,12 @@
         <v>+51 955 121 011</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C189" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D189">
         <v>51</v>
@@ -4865,12 +4866,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>104</v>
       </c>
       <c r="C190" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D190">
         <v>52</v>
@@ -4880,15 +4881,15 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>152</v>
       </c>
       <c r="B191" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C191" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D191">
         <v>52</v>
@@ -4898,12 +4899,12 @@
         <v>+52  1 479 233 6442</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>103</v>
       </c>
       <c r="C192" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D192">
         <v>51</v>
@@ -4913,12 +4914,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C193" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D193">
         <v>51</v>
@@ -4928,12 +4929,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>80</v>
       </c>
       <c r="C194" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D194">
         <v>51</v>
@@ -4943,15 +4944,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B195" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C195" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D195">
         <v>52</v>
@@ -4961,12 +4962,12 @@
         <v>+52  1 756 103 6825</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C196" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D196">
         <v>58</v>
@@ -4976,12 +4977,12 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C197" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D197">
         <v>51</v>
@@ -4991,15 +4992,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B198" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C198" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D198">
         <v>52</v>
@@ -5009,15 +5010,15 @@
         <v>+52  1 981 217 7384</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>48</v>
       </c>
       <c r="B199" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C199" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D199">
         <v>52</v>
@@ -5027,12 +5028,12 @@
         <v>+52 1 231 176 9718</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C200" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D200">
         <v>52</v>
@@ -5042,15 +5043,15 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B201" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C201" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D201">
         <v>52</v>
@@ -5060,12 +5061,12 @@
         <v>+52  1 55 7364 9786</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>151</v>
       </c>
       <c r="C202" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D202">
         <v>56</v>
@@ -5075,12 +5076,12 @@
         <v xml:space="preserve">+56 </v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C203" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D203">
         <v>51</v>
@@ -5090,15 +5091,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B204" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C204" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D204">
         <v>53</v>
@@ -5108,12 +5109,12 @@
         <v>+53 5 1795768</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>96</v>
       </c>
       <c r="C205" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D205">
         <v>51</v>
@@ -5123,15 +5124,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B206" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C206" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D206">
         <v>58</v>
@@ -5141,12 +5142,12 @@
         <v>+58 414-8694655</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>97</v>
       </c>
       <c r="C207" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D207">
         <v>51</v>
@@ -5156,15 +5157,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>28</v>
       </c>
       <c r="B208" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C208" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D208">
         <v>51</v>
@@ -5174,12 +5175,12 @@
         <v>+51 981 000 049</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C209" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D209">
         <v>51</v>
@@ -5189,15 +5190,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>145</v>
       </c>
       <c r="B210" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C210" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D210">
         <v>56</v>
@@ -5207,15 +5208,15 @@
         <v>+56 9 7878 6558</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>7</v>
       </c>
       <c r="B211" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C211" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D211">
         <v>51</v>
@@ -5225,15 +5226,15 @@
         <v>+51 973 614 848</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>15</v>
       </c>
       <c r="B212" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C212" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D212">
         <v>51</v>
@@ -5243,12 +5244,12 @@
         <v>+51 971 942 638</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C213" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D213">
         <v>51</v>
@@ -5258,15 +5259,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>40</v>
       </c>
       <c r="B214" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C214" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D214">
         <v>58</v>
@@ -5276,12 +5277,12 @@
         <v>+58 422-0376517</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>91</v>
       </c>
       <c r="C215" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D215">
         <v>51</v>
@@ -5291,15 +5292,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B216" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C216" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D216">
         <v>52</v>
@@ -5309,15 +5310,15 @@
         <v>+52  1 834 252 9665</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>14</v>
       </c>
       <c r="B217" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C217" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D217">
         <v>506</v>
@@ -5327,12 +5328,12 @@
         <v>+506 6082 6653</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>67</v>
       </c>
       <c r="C218" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D218">
         <v>503</v>
@@ -5342,12 +5343,12 @@
         <v xml:space="preserve">+503 </v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>116</v>
       </c>
       <c r="C219" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D219">
         <v>54</v>
@@ -5357,15 +5358,15 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C220" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D220">
         <v>51</v>
@@ -5375,15 +5376,15 @@
         <v>+51 992 958 823</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>148</v>
       </c>
       <c r="B221" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C221" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D221">
         <v>58</v>
@@ -5393,12 +5394,12 @@
         <v>+58 412-5885303</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>98</v>
       </c>
       <c r="C222" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D222">
         <v>54</v>
@@ -5408,12 +5409,12 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C223" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D223">
         <v>51</v>
@@ -5423,12 +5424,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>79</v>
       </c>
       <c r="C224" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D224">
         <v>51</v>
@@ -5438,15 +5439,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>60</v>
       </c>
       <c r="B225" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C225" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D225">
         <v>58</v>
@@ -5456,15 +5457,15 @@
         <v>+58 414-7234994</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B226" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C226" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D226">
         <v>1</v>
@@ -5474,15 +5475,15 @@
         <v>+1 849 763-2529</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B227" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C227" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D227">
         <v>52</v>
@@ -5492,12 +5493,12 @@
         <v>+52 1 56 3172 0225</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>6</v>
       </c>
       <c r="C228" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D228">
         <v>51</v>
@@ -5507,12 +5508,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>36</v>
       </c>
       <c r="C229" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D229">
         <v>51</v>
@@ -5522,12 +5523,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>123</v>
       </c>
       <c r="C230" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D230">
         <v>54</v>
@@ -5537,12 +5538,12 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>73</v>
       </c>
       <c r="C231" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D231">
         <v>51</v>
@@ -5552,12 +5553,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>85</v>
       </c>
       <c r="C232" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D232">
         <v>51</v>
@@ -5567,12 +5568,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C233" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D233">
         <v>54</v>
@@ -5582,12 +5583,12 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>143</v>
       </c>
       <c r="C234" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D234">
         <v>54</v>
@@ -5597,12 +5598,12 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C235" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D235">
         <v>52</v>
@@ -5612,15 +5613,15 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B236" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C236" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D236">
         <v>51</v>
@@ -5630,12 +5631,12 @@
         <v>+51 923 404 224</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>81</v>
       </c>
       <c r="C237" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D237">
         <v>51</v>
@@ -5645,15 +5646,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>19</v>
       </c>
       <c r="B238" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C238" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D238">
         <v>51</v>
@@ -5663,7 +5664,7 @@
         <v>+51 987 200 136</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>13</v>
       </c>
@@ -5671,7 +5672,7 @@
         <v>972691544</v>
       </c>
       <c r="C239" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D239">
         <v>51</v>
@@ -5681,15 +5682,15 @@
         <v>+51 972691544</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B240" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C240" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D240">
         <v>53</v>
@@ -5699,12 +5700,12 @@
         <v>+53  5 2756474</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C241" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D241">
         <v>52</v>
@@ -5714,12 +5715,12 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C242" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D242">
         <v>54</v>
@@ -5729,12 +5730,12 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>131</v>
       </c>
       <c r="C243" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D243">
         <v>51</v>
@@ -5744,12 +5745,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C244" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D244">
         <v>54</v>
@@ -5759,12 +5760,12 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>76</v>
       </c>
       <c r="C245" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D245">
         <v>51</v>
@@ -5774,12 +5775,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>49</v>
       </c>
       <c r="C246" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D246">
         <v>51</v>
@@ -5789,15 +5790,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>24</v>
       </c>
       <c r="B247" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C247" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D247">
         <v>51</v>
@@ -5807,15 +5808,15 @@
         <v>+51 937 332 268</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>102</v>
       </c>
       <c r="B248" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C248" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D248">
         <v>51</v>
@@ -5825,15 +5826,15 @@
         <v>+51 955 963 610</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B249" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C249" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D249">
         <v>51</v>
@@ -5843,12 +5844,12 @@
         <v>+51 931 252 452</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C250" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D250">
         <v>51</v>
@@ -5858,12 +5859,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>82</v>
       </c>
       <c r="C251" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D251">
         <v>51</v>
@@ -5873,15 +5874,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1</v>
       </c>
       <c r="B252" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C252" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D252">
         <v>51</v>
@@ -5891,12 +5892,12 @@
         <v>+51 945 323 097</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C253" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D253">
         <v>52</v>
@@ -5906,15 +5907,15 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>63</v>
       </c>
       <c r="B254" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C254" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D254">
         <v>51</v>
@@ -5924,15 +5925,15 @@
         <v>+51 965 373 102</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B255" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C255" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D255">
         <v>52</v>
@@ -5942,15 +5943,15 @@
         <v>+52 1 916 116 9432</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B256" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C256" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D256">
         <v>52</v>
@@ -5960,12 +5961,12 @@
         <v>+52  1 771 112 3061</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C257" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D257">
         <v>58</v>
@@ -5975,15 +5976,15 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>70</v>
       </c>
       <c r="B258" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C258" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D258">
         <v>51</v>
@@ -5993,12 +5994,12 @@
         <v>+51 955 834 817</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>144</v>
       </c>
       <c r="C259" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D259">
         <v>52</v>
@@ -6008,12 +6009,12 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>95</v>
       </c>
       <c r="C260" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D260">
         <v>52</v>
@@ -6023,15 +6024,15 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>62</v>
       </c>
       <c r="B261" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C261" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D261">
         <v>54</v>
@@ -6041,15 +6042,15 @@
         <v>+54 9 3794 12-0368</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>11</v>
       </c>
       <c r="B262" t="s">
+        <v>356</v>
+      </c>
+      <c r="C262" t="s">
         <v>357</v>
-      </c>
-      <c r="C262" t="s">
-        <v>358</v>
       </c>
       <c r="D262">
         <v>502</v>
@@ -6059,15 +6060,15 @@
         <v>+502 4760 5947</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
+        <v>402</v>
+      </c>
+      <c r="B263" t="s">
         <v>403</v>
       </c>
-      <c r="B263" t="s">
-        <v>404</v>
-      </c>
       <c r="C263" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D263">
         <v>57</v>
@@ -6077,15 +6078,15 @@
         <v>+57 333 2913156</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
+        <v>404</v>
+      </c>
+      <c r="B264" t="s">
         <v>405</v>
       </c>
-      <c r="B264" t="s">
-        <v>406</v>
-      </c>
       <c r="C264" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D264">
         <v>54</v>
@@ -6095,12 +6096,12 @@
         <v>+54 9 11 2507-8576</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C265" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D265">
         <v>51</v>
@@ -6110,15 +6111,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B266" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C266" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D266">
         <v>51</v>
@@ -6128,15 +6129,15 @@
         <v>+51  982 638 611</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
+        <v>413</v>
+      </c>
+      <c r="B267" t="s">
         <v>414</v>
       </c>
-      <c r="B267" t="s">
-        <v>415</v>
-      </c>
       <c r="C267" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D267">
         <v>58</v>
@@ -6146,15 +6147,15 @@
         <v>+58 412-8286364</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
+        <v>415</v>
+      </c>
+      <c r="B268" t="s">
         <v>416</v>
       </c>
-      <c r="B268" t="s">
-        <v>417</v>
-      </c>
       <c r="C268" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D268">
         <v>503</v>
@@ -6164,15 +6165,15 @@
         <v>+503 7279 9978</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C269" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D269">
         <v>51</v>
@@ -6183,7 +6184,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E269" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}"/>
+  <autoFilter ref="A1:E269" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="masafesio"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A262">
     <sortCondition ref="A2:A262"/>
   </sortState>

--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BC758B-F85C-4330-8E68-C383A3BB7EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1B2C7B-C3D3-48A0-9F09-4EE9F65D9B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="431">
   <si>
     <t>Darmanethan</t>
   </si>
@@ -1318,6 +1318,18 @@
   </si>
   <si>
     <t>darkam580</t>
+  </si>
+  <si>
+    <t>Jayr</t>
+  </si>
+  <si>
+    <t>Rodolfo Ram</t>
+  </si>
+  <si>
+    <t>Arabia Saudit</t>
+  </si>
+  <si>
+    <t>966 545039929</t>
   </si>
 </sst>
 </file>
@@ -1693,8 +1705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:E269"/>
+  <dimension ref="A1:E272"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
@@ -1719,7 +1730,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -1734,7 +1745,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>234</v>
       </c>
@@ -1752,7 +1763,7 @@
         <v>+51 933 668 277</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>41</v>
       </c>
@@ -1770,7 +1781,7 @@
         <v>+51 980 596 555</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -1788,7 +1799,7 @@
         <v>+58 424-7086947</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>83</v>
       </c>
@@ -1803,7 +1814,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>233</v>
       </c>
@@ -1821,7 +1832,7 @@
         <v>+58 412-1322018</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>191</v>
       </c>
@@ -1839,7 +1850,7 @@
         <v>+56 9 7927 3083</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>113</v>
       </c>
@@ -1854,7 +1865,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1872,7 +1883,7 @@
         <v>+51 985 699 608</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -1890,7 +1901,7 @@
         <v>+52 1 56 1007 9583</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>189</v>
       </c>
@@ -1908,7 +1919,7 @@
         <v>+52 1 81 2944 2313</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>84</v>
       </c>
@@ -1923,7 +1934,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>92</v>
       </c>
@@ -1938,7 +1949,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>159</v>
       </c>
@@ -1953,7 +1964,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -1971,7 +1982,7 @@
         <v>+51  984 190 584</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>149</v>
       </c>
@@ -1986,7 +1997,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -2004,7 +2015,7 @@
         <v>+51 984 267 160</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -2022,7 +2033,7 @@
         <v>+51  912 858 811</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>127</v>
       </c>
@@ -2037,7 +2048,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>136</v>
       </c>
@@ -2055,7 +2066,7 @@
         <v>+51 949 647 819</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -2073,7 +2084,7 @@
         <v>+34  646 20 50 99</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>226</v>
       </c>
@@ -2088,7 +2099,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>137</v>
       </c>
@@ -2106,7 +2117,7 @@
         <v>+52  1 222 102 8165</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -2124,7 +2135,7 @@
         <v>+58 416-4398466</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>129</v>
       </c>
@@ -2142,7 +2153,7 @@
         <v>+54 91139028131</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -2160,7 +2171,7 @@
         <v>+57 322 4761144</v>
       </c>
     </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -2178,7 +2189,7 @@
         <v>+52 1 771 306 4084</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>232</v>
       </c>
@@ -2196,7 +2207,7 @@
         <v>+58 412-7060529</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -2214,7 +2225,7 @@
         <v>+51 933448842</v>
       </c>
     </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>37</v>
       </c>
@@ -2229,7 +2240,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -2247,7 +2258,7 @@
         <v>+51 912358537</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>178</v>
       </c>
@@ -2265,7 +2276,7 @@
         <v>+51 950 746 501</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>54</v>
       </c>
@@ -2283,7 +2294,7 @@
         <v>+54 9 3794 73 7373</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>119</v>
       </c>
@@ -2298,7 +2309,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>424</v>
       </c>
@@ -2316,7 +2327,7 @@
         <v>+55 71 9370-7438</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>252</v>
       </c>
@@ -2334,7 +2345,7 @@
         <v>+51 991 176 689</v>
       </c>
     </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>121</v>
       </c>
@@ -2352,7 +2363,7 @@
         <v>+34 601 36 84 69</v>
       </c>
     </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>71</v>
       </c>
@@ -2367,7 +2378,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>182</v>
       </c>
@@ -2385,7 +2396,7 @@
         <v>+51  917 057 695</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>51</v>
       </c>
@@ -2403,7 +2414,7 @@
         <v>+34 608 39 51 22</v>
       </c>
     </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>219</v>
       </c>
@@ -2418,7 +2429,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>117</v>
       </c>
@@ -2433,7 +2444,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>99</v>
       </c>
@@ -2448,7 +2459,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>196</v>
       </c>
@@ -2466,7 +2477,7 @@
         <v>+54 93854880470</v>
       </c>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>61</v>
       </c>
@@ -2484,7 +2495,7 @@
         <v>+53 51162846</v>
       </c>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>168</v>
       </c>
@@ -2499,7 +2510,7 @@
         <v xml:space="preserve">+1 </v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>57</v>
       </c>
@@ -2514,7 +2525,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>10</v>
       </c>
@@ -2532,7 +2543,7 @@
         <v>+51  920 449 371</v>
       </c>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>68</v>
       </c>
@@ -2550,7 +2561,7 @@
         <v>+51  912 209 142</v>
       </c>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>105</v>
       </c>
@@ -2565,7 +2576,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>0</v>
       </c>
@@ -2583,7 +2594,7 @@
         <v>+505 8799 9543</v>
       </c>
     </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>125</v>
       </c>
@@ -2601,7 +2612,7 @@
         <v>+52 1 686 589 5829</v>
       </c>
     </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>160</v>
       </c>
@@ -2619,7 +2630,7 @@
         <v>+51 992 067 030</v>
       </c>
     </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>108</v>
       </c>
@@ -2634,7 +2645,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -2649,7 +2660,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>228</v>
       </c>
@@ -2664,7 +2675,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>32</v>
       </c>
@@ -2682,7 +2693,7 @@
         <v>+58  412-7396859</v>
       </c>
     </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>111</v>
       </c>
@@ -2700,7 +2711,7 @@
         <v>+52 1 921 208 0809</v>
       </c>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>100</v>
       </c>
@@ -2715,7 +2726,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>165</v>
       </c>
@@ -2733,7 +2744,7 @@
         <v>+504 3204-1711</v>
       </c>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>128</v>
       </c>
@@ -2751,7 +2762,7 @@
         <v>+56 99797773</v>
       </c>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>220</v>
       </c>
@@ -2766,7 +2777,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>39</v>
       </c>
@@ -2784,7 +2795,7 @@
         <v>+1 305 8902347</v>
       </c>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>406</v>
       </c>
@@ -2802,7 +2813,7 @@
         <v>+52 1 861 128 3193</v>
       </c>
     </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>124</v>
       </c>
@@ -2817,7 +2828,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>175</v>
       </c>
@@ -2832,7 +2843,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>214</v>
       </c>
@@ -2850,7 +2861,7 @@
         <v>+52 8341048014</v>
       </c>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>5</v>
       </c>
@@ -2868,7 +2879,7 @@
         <v>+506  8936 2350</v>
       </c>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>158</v>
       </c>
@@ -2886,7 +2897,7 @@
         <v>+1 253 212-8032</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -2904,7 +2915,7 @@
         <v>+51 991 846 357</v>
       </c>
     </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>192</v>
       </c>
@@ -2922,7 +2933,7 @@
         <v>+52 1 33 4442 1918</v>
       </c>
     </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>110</v>
       </c>
@@ -2937,7 +2948,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>185</v>
       </c>
@@ -2952,7 +2963,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>238</v>
       </c>
@@ -2967,7 +2978,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>31</v>
       </c>
@@ -2985,7 +2996,7 @@
         <v>+51  912 058 374</v>
       </c>
     </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>88</v>
       </c>
@@ -3000,7 +3011,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>133</v>
       </c>
@@ -3015,7 +3026,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>90</v>
       </c>
@@ -3030,7 +3041,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>106</v>
       </c>
@@ -3045,7 +3056,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>212</v>
       </c>
@@ -3063,7 +3074,7 @@
         <v>+593  96 083 0485</v>
       </c>
     </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>112</v>
       </c>
@@ -3078,7 +3089,7 @@
         <v xml:space="preserve">+505 </v>
       </c>
     </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>107</v>
       </c>
@@ -3093,7 +3104,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>44</v>
       </c>
@@ -3111,7 +3122,7 @@
         <v>+51  983 379 394</v>
       </c>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>66</v>
       </c>
@@ -3126,7 +3137,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>161</v>
       </c>
@@ -3144,7 +3155,7 @@
         <v>+51 980 679 898</v>
       </c>
     </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>227</v>
       </c>
@@ -3159,7 +3170,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>139</v>
       </c>
@@ -3177,7 +3188,7 @@
         <v>+53  5 6467775</v>
       </c>
     </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>174</v>
       </c>
@@ -3195,7 +3206,7 @@
         <v>+51 943126988</v>
       </c>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>122</v>
       </c>
@@ -3210,7 +3221,7 @@
         <v xml:space="preserve">+593 </v>
       </c>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>211</v>
       </c>
@@ -3225,7 +3236,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>45</v>
       </c>
@@ -3243,7 +3254,7 @@
         <v>+54 9 3412 81-3587</v>
       </c>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>89</v>
       </c>
@@ -3258,7 +3269,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>120</v>
       </c>
@@ -3276,7 +3287,7 @@
         <v>+57  302 5578252</v>
       </c>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>203</v>
       </c>
@@ -3294,7 +3305,7 @@
         <v>+593 96 151 5565</v>
       </c>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>241</v>
       </c>
@@ -3312,7 +3323,7 @@
         <v>+51 956 677 392</v>
       </c>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>237</v>
       </c>
@@ -3330,7 +3341,7 @@
         <v>+54 9 11 2783 9968</v>
       </c>
     </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>154</v>
       </c>
@@ -3348,7 +3359,7 @@
         <v>+51 961 492 733</v>
       </c>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>34</v>
       </c>
@@ -3366,7 +3377,7 @@
         <v>+53 5 1113536</v>
       </c>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>140</v>
       </c>
@@ -3381,7 +3392,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>230</v>
       </c>
@@ -3396,7 +3407,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>141</v>
       </c>
@@ -3411,7 +3422,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>55</v>
       </c>
@@ -3429,7 +3440,7 @@
         <v>+1 809 658-5500</v>
       </c>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>153</v>
       </c>
@@ -3447,7 +3458,7 @@
         <v>+58 424-1216695</v>
       </c>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>167</v>
       </c>
@@ -3465,7 +3476,7 @@
         <v>+51 963 745 855</v>
       </c>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>222</v>
       </c>
@@ -3483,7 +3494,7 @@
         <v>+51  960 274 071</v>
       </c>
     </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>114</v>
       </c>
@@ -3501,7 +3512,7 @@
         <v>+593 98 768 2900</v>
       </c>
     </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>94</v>
       </c>
@@ -3516,7 +3527,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>244</v>
       </c>
@@ -3534,7 +3545,7 @@
         <v>+503 7868 0662</v>
       </c>
     </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>240</v>
       </c>
@@ -3549,7 +3560,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>155</v>
       </c>
@@ -3567,7 +3578,7 @@
         <v>+58 414-4473628</v>
       </c>
     </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>43</v>
       </c>
@@ -3585,7 +3596,7 @@
         <v>+57 3054850698</v>
       </c>
     </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>221</v>
       </c>
@@ -3600,7 +3611,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>162</v>
       </c>
@@ -3615,7 +3626,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>56</v>
       </c>
@@ -3630,7 +3641,7 @@
         <v xml:space="preserve">+507 </v>
       </c>
     </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>150</v>
       </c>
@@ -3648,7 +3659,7 @@
         <v>+58  412-1885430</v>
       </c>
     </row>
-    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>130</v>
       </c>
@@ -3666,7 +3677,7 @@
         <v>+51  906 691 465</v>
       </c>
     </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>146</v>
       </c>
@@ -3681,7 +3692,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>164</v>
       </c>
@@ -3699,7 +3710,7 @@
         <v>+1  787 513-4231</v>
       </c>
     </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>46</v>
       </c>
@@ -3717,7 +3728,7 @@
         <v>+507  6898-7574</v>
       </c>
     </row>
-    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>207</v>
       </c>
@@ -3735,7 +3746,7 @@
         <v>+52 1 444 674 9780</v>
       </c>
     </row>
-    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>2</v>
       </c>
@@ -3750,7 +3761,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>21</v>
       </c>
@@ -3768,7 +3779,7 @@
         <v>+51 996 668 615</v>
       </c>
     </row>
-    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>77</v>
       </c>
@@ -3783,7 +3794,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>247</v>
       </c>
@@ -3801,7 +3812,7 @@
         <v>+52 1 55 3845 6274</v>
       </c>
     </row>
-    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>190</v>
       </c>
@@ -3816,7 +3827,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>251</v>
       </c>
@@ -3834,7 +3845,7 @@
         <v>+51  921 447 908</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>12</v>
       </c>
@@ -3852,7 +3863,7 @@
         <v>+51 976 413 331</v>
       </c>
     </row>
-    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>181</v>
       </c>
@@ -3867,7 +3878,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>101</v>
       </c>
@@ -3882,7 +3893,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>156</v>
       </c>
@@ -3897,7 +3908,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>47</v>
       </c>
@@ -3912,7 +3923,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>218</v>
       </c>
@@ -3930,7 +3941,7 @@
         <v>+52 Juni Frostheart</v>
       </c>
     </row>
-    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>255</v>
       </c>
@@ -3948,7 +3959,7 @@
         <v>+54 9 11 2526 8333</v>
       </c>
     </row>
-    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>245</v>
       </c>
@@ -3966,7 +3977,7 @@
         <v>+51 963 347 387</v>
       </c>
     </row>
-    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>33</v>
       </c>
@@ -3984,7 +3995,7 @@
         <v>+52 1 81 2684 3183</v>
       </c>
     </row>
-    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>135</v>
       </c>
@@ -3999,7 +4010,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>177</v>
       </c>
@@ -4014,7 +4025,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>109</v>
       </c>
@@ -4029,7 +4040,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>142</v>
       </c>
@@ -4044,7 +4055,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>26</v>
       </c>
@@ -4062,7 +4073,7 @@
         <v>+57 302 3773516</v>
       </c>
     </row>
-    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -4080,7 +4091,7 @@
         <v>+54  9 11 2372-2211</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>209</v>
       </c>
@@ -4098,7 +4109,7 @@
         <v>+51 960 749 072</v>
       </c>
     </row>
-    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>25</v>
       </c>
@@ -4116,7 +4127,7 @@
         <v>+51 984 784 816</v>
       </c>
     </row>
-    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>242</v>
       </c>
@@ -4134,7 +4145,7 @@
         <v>+51 986 579 683</v>
       </c>
     </row>
-    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>205</v>
       </c>
@@ -4152,7 +4163,7 @@
         <v>+52 1 614 529 6392</v>
       </c>
     </row>
-    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>208</v>
       </c>
@@ -4170,7 +4181,7 @@
         <v>+52 1 287 154 7879</v>
       </c>
     </row>
-    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>173</v>
       </c>
@@ -4185,7 +4196,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>183</v>
       </c>
@@ -4200,7 +4211,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>65</v>
       </c>
@@ -4218,7 +4229,7 @@
         <v>+593 98 174 5020</v>
       </c>
     </row>
-    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>4</v>
       </c>
@@ -4233,7 +4244,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>118</v>
       </c>
@@ -4248,7 +4259,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>171</v>
       </c>
@@ -4266,7 +4277,7 @@
         <v>+52 1 771 297 6010</v>
       </c>
     </row>
-    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>176</v>
       </c>
@@ -4281,7 +4292,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>186</v>
       </c>
@@ -4299,7 +4310,7 @@
         <v>+52  1 983 752 2450</v>
       </c>
     </row>
-    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>93</v>
       </c>
@@ -4332,7 +4343,7 @@
         <v>+58 424-6956750</v>
       </c>
     </row>
-    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>72</v>
       </c>
@@ -4350,7 +4361,7 @@
         <v>+51  965 337 810</v>
       </c>
     </row>
-    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>86</v>
       </c>
@@ -4365,7 +4376,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>87</v>
       </c>
@@ -4380,7 +4391,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>75</v>
       </c>
@@ -4395,7 +4406,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>198</v>
       </c>
@@ -4410,7 +4421,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>250</v>
       </c>
@@ -4428,7 +4439,7 @@
         <v>+51  945 349 568</v>
       </c>
     </row>
-    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>249</v>
       </c>
@@ -4446,7 +4457,7 @@
         <v>+52 1 735 162 2046</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>243</v>
       </c>
@@ -4464,7 +4475,7 @@
         <v>+51 970 857 085</v>
       </c>
     </row>
-    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>78</v>
       </c>
@@ -4479,7 +4490,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>147</v>
       </c>
@@ -4497,7 +4508,7 @@
         <v>+52  1 673 472 3074</v>
       </c>
     </row>
-    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>59</v>
       </c>
@@ -4515,7 +4526,7 @@
         <v>+54 9 2974 22-6785</v>
       </c>
     </row>
-    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>239</v>
       </c>
@@ -4533,7 +4544,7 @@
         <v>+52 1 55 1805 8456</v>
       </c>
     </row>
-    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>231</v>
       </c>
@@ -4548,7 +4559,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>35</v>
       </c>
@@ -4566,7 +4577,7 @@
         <v>+54  9 11 6135-9811</v>
       </c>
     </row>
-    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>199</v>
       </c>
@@ -4581,7 +4592,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>216</v>
       </c>
@@ -4599,7 +4610,7 @@
         <v>+51 991 342 085</v>
       </c>
     </row>
-    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>69</v>
       </c>
@@ -4614,7 +4625,7 @@
         <v xml:space="preserve">+506 </v>
       </c>
     </row>
-    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>215</v>
       </c>
@@ -4629,7 +4640,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>166</v>
       </c>
@@ -4644,7 +4655,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>254</v>
       </c>
@@ -4662,7 +4673,7 @@
         <v>+53 5 6957902</v>
       </c>
     </row>
-    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>134</v>
       </c>
@@ -4677,7 +4688,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>132</v>
       </c>
@@ -4692,7 +4703,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>29</v>
       </c>
@@ -4710,7 +4721,7 @@
         <v>+51 977 404 957</v>
       </c>
     </row>
-    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>53</v>
       </c>
@@ -4728,7 +4739,7 @@
         <v>+52 1 229 229 9515</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>64</v>
       </c>
@@ -4746,7 +4757,7 @@
         <v>+51 986 824 543</v>
       </c>
     </row>
-    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>16</v>
       </c>
@@ -4764,7 +4775,7 @@
         <v>+591 69865757</v>
       </c>
     </row>
-    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>58</v>
       </c>
@@ -4782,7 +4793,7 @@
         <v>+506  7139 5493</v>
       </c>
     </row>
-    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>115</v>
       </c>
@@ -4797,7 +4808,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>195</v>
       </c>
@@ -4815,7 +4826,7 @@
         <v>+58 424-2233503</v>
       </c>
     </row>
-    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>204</v>
       </c>
@@ -4833,7 +4844,7 @@
         <v>+52 6644057270</v>
       </c>
     </row>
-    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>3</v>
       </c>
@@ -4851,7 +4862,7 @@
         <v>+51 955 121 011</v>
       </c>
     </row>
-    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>170</v>
       </c>
@@ -4866,7 +4877,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>104</v>
       </c>
@@ -4881,7 +4892,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>152</v>
       </c>
@@ -4899,7 +4910,7 @@
         <v>+52  1 479 233 6442</v>
       </c>
     </row>
-    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>103</v>
       </c>
@@ -4914,7 +4925,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>256</v>
       </c>
@@ -4929,7 +4940,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>80</v>
       </c>
@@ -4944,7 +4955,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>187</v>
       </c>
@@ -4962,7 +4973,7 @@
         <v>+52  1 756 103 6825</v>
       </c>
     </row>
-    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>201</v>
       </c>
@@ -4977,7 +4988,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>172</v>
       </c>
@@ -4992,7 +5003,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>200</v>
       </c>
@@ -5010,7 +5021,7 @@
         <v>+52  1 981 217 7384</v>
       </c>
     </row>
-    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>48</v>
       </c>
@@ -5028,7 +5039,7 @@
         <v>+52 1 231 176 9718</v>
       </c>
     </row>
-    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>246</v>
       </c>
@@ -5043,7 +5054,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>197</v>
       </c>
@@ -5061,7 +5072,7 @@
         <v>+52  1 55 7364 9786</v>
       </c>
     </row>
-    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>151</v>
       </c>
@@ -5076,7 +5087,7 @@
         <v xml:space="preserve">+56 </v>
       </c>
     </row>
-    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>180</v>
       </c>
@@ -5091,7 +5102,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>193</v>
       </c>
@@ -5109,7 +5120,7 @@
         <v>+53 5 1795768</v>
       </c>
     </row>
-    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>96</v>
       </c>
@@ -5124,7 +5135,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>248</v>
       </c>
@@ -5142,7 +5153,7 @@
         <v>+58 414-8694655</v>
       </c>
     </row>
-    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>97</v>
       </c>
@@ -5157,7 +5168,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>28</v>
       </c>
@@ -5175,7 +5186,7 @@
         <v>+51 981 000 049</v>
       </c>
     </row>
-    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>188</v>
       </c>
@@ -5190,7 +5201,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>145</v>
       </c>
@@ -5208,7 +5219,7 @@
         <v>+56 9 7878 6558</v>
       </c>
     </row>
-    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>7</v>
       </c>
@@ -5226,7 +5237,7 @@
         <v>+51 973 614 848</v>
       </c>
     </row>
-    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>15</v>
       </c>
@@ -5244,7 +5255,7 @@
         <v>+51 971 942 638</v>
       </c>
     </row>
-    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>235</v>
       </c>
@@ -5259,7 +5270,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>40</v>
       </c>
@@ -5277,7 +5288,7 @@
         <v>+58 422-0376517</v>
       </c>
     </row>
-    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>91</v>
       </c>
@@ -5292,7 +5303,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>224</v>
       </c>
@@ -5310,7 +5321,7 @@
         <v>+52  1 834 252 9665</v>
       </c>
     </row>
-    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>14</v>
       </c>
@@ -5328,7 +5339,7 @@
         <v>+506 6082 6653</v>
       </c>
     </row>
-    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>67</v>
       </c>
@@ -5343,7 +5354,7 @@
         <v xml:space="preserve">+503 </v>
       </c>
     </row>
-    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>116</v>
       </c>
@@ -5358,7 +5369,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>163</v>
       </c>
@@ -5376,7 +5387,7 @@
         <v>+51 992 958 823</v>
       </c>
     </row>
-    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>148</v>
       </c>
@@ -5394,7 +5405,7 @@
         <v>+58 412-5885303</v>
       </c>
     </row>
-    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>98</v>
       </c>
@@ -5409,7 +5420,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>257</v>
       </c>
@@ -5424,7 +5435,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>79</v>
       </c>
@@ -5439,7 +5450,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>60</v>
       </c>
@@ -5457,7 +5468,7 @@
         <v>+58 414-7234994</v>
       </c>
     </row>
-    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>157</v>
       </c>
@@ -5475,7 +5486,7 @@
         <v>+1 849 763-2529</v>
       </c>
     </row>
-    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>194</v>
       </c>
@@ -5493,7 +5504,7 @@
         <v>+52 1 56 3172 0225</v>
       </c>
     </row>
-    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>6</v>
       </c>
@@ -5508,7 +5519,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>36</v>
       </c>
@@ -5523,7 +5534,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>123</v>
       </c>
@@ -5538,7 +5549,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>73</v>
       </c>
@@ -5553,7 +5564,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>85</v>
       </c>
@@ -5568,7 +5579,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>223</v>
       </c>
@@ -5583,7 +5594,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>143</v>
       </c>
@@ -5598,7 +5609,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>217</v>
       </c>
@@ -5613,7 +5624,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>253</v>
       </c>
@@ -5631,7 +5642,7 @@
         <v>+51 923 404 224</v>
       </c>
     </row>
-    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>81</v>
       </c>
@@ -5646,7 +5657,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>19</v>
       </c>
@@ -5664,7 +5675,7 @@
         <v>+51 987 200 136</v>
       </c>
     </row>
-    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>13</v>
       </c>
@@ -5682,7 +5693,7 @@
         <v>+51 972691544</v>
       </c>
     </row>
-    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>184</v>
       </c>
@@ -5700,7 +5711,7 @@
         <v>+53  5 2756474</v>
       </c>
     </row>
-    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>202</v>
       </c>
@@ -5715,7 +5726,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>210</v>
       </c>
@@ -5730,7 +5741,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>131</v>
       </c>
@@ -5745,7 +5756,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>229</v>
       </c>
@@ -5760,7 +5771,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>76</v>
       </c>
@@ -5775,7 +5786,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>49</v>
       </c>
@@ -5790,7 +5801,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>24</v>
       </c>
@@ -5808,7 +5819,7 @@
         <v>+51 937 332 268</v>
       </c>
     </row>
-    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>102</v>
       </c>
@@ -5826,7 +5837,7 @@
         <v>+51 955 963 610</v>
       </c>
     </row>
-    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>169</v>
       </c>
@@ -5844,7 +5855,7 @@
         <v>+51 931 252 452</v>
       </c>
     </row>
-    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>179</v>
       </c>
@@ -5859,7 +5870,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>82</v>
       </c>
@@ -5874,7 +5885,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1</v>
       </c>
@@ -5892,7 +5903,7 @@
         <v>+51 945 323 097</v>
       </c>
     </row>
-    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>206</v>
       </c>
@@ -5907,7 +5918,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>63</v>
       </c>
@@ -5925,7 +5936,7 @@
         <v>+51 965 373 102</v>
       </c>
     </row>
-    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>225</v>
       </c>
@@ -5943,7 +5954,7 @@
         <v>+52 1 916 116 9432</v>
       </c>
     </row>
-    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>236</v>
       </c>
@@ -5961,7 +5972,7 @@
         <v>+52  1 771 112 3061</v>
       </c>
     </row>
-    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>213</v>
       </c>
@@ -5976,7 +5987,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>70</v>
       </c>
@@ -5994,7 +6005,7 @@
         <v>+51 955 834 817</v>
       </c>
     </row>
-    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>144</v>
       </c>
@@ -6009,7 +6020,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>95</v>
       </c>
@@ -6024,7 +6035,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>62</v>
       </c>
@@ -6042,7 +6053,7 @@
         <v>+54 9 3794 12-0368</v>
       </c>
     </row>
-    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>11</v>
       </c>
@@ -6060,7 +6071,7 @@
         <v>+502 4760 5947</v>
       </c>
     </row>
-    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>402</v>
       </c>
@@ -6078,7 +6089,7 @@
         <v>+57 333 2913156</v>
       </c>
     </row>
-    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>404</v>
       </c>
@@ -6096,7 +6107,7 @@
         <v>+54 9 11 2507-8576</v>
       </c>
     </row>
-    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>407</v>
       </c>
@@ -6111,7 +6122,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>408</v>
       </c>
@@ -6129,7 +6140,7 @@
         <v>+51  982 638 611</v>
       </c>
     </row>
-    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>413</v>
       </c>
@@ -6143,11 +6154,11 @@
         <v>58</v>
       </c>
       <c r="E267" t="str">
-        <f t="shared" ref="E267:E269" si="7">CONCATENATE("+",D267," ",B267)</f>
+        <f t="shared" ref="E267:E272" si="7">CONCATENATE("+",D267," ",B267)</f>
         <v>+58 412-8286364</v>
       </c>
     </row>
-    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>415</v>
       </c>
@@ -6165,7 +6176,7 @@
         <v>+503 7279 9978</v>
       </c>
     </row>
-    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>418</v>
       </c>
@@ -6183,18 +6194,51 @@
         <v>+51 964 533 667</v>
       </c>
     </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>427</v>
+      </c>
+      <c r="B270" t="s">
+        <v>430</v>
+      </c>
+      <c r="C270" t="s">
+        <v>429</v>
+      </c>
+      <c r="E270" t="str">
+        <f t="shared" si="7"/>
+        <v>+ 966 545039929</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>428</v>
+      </c>
+      <c r="B271">
+        <v>8781577661</v>
+      </c>
+      <c r="C271" t="s">
+        <v>265</v>
+      </c>
+      <c r="D271">
+        <v>52</v>
+      </c>
+      <c r="E271" t="str">
+        <f t="shared" si="7"/>
+        <v>+52 8781577661</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E272" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">+ </v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E269" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="masafesio"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:E269" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A262">
     <sortCondition ref="A2:A262"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1B2C7B-C3D3-48A0-9F09-4EE9F65D9B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15402F95-9C1F-43DB-954D-54833D934247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="432">
   <si>
     <t>Darmanethan</t>
   </si>
@@ -1329,7 +1329,10 @@
     <t>Arabia Saudit</t>
   </si>
   <si>
-    <t>966 545039929</t>
+    <t>Shotper</t>
+  </si>
+  <si>
+    <t>DarkM17</t>
   </si>
 </sst>
 </file>
@@ -1705,7 +1708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
-  <dimension ref="A1:E272"/>
+  <dimension ref="A1:E273"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
@@ -6111,6 +6114,9 @@
       <c r="A265" t="s">
         <v>407</v>
       </c>
+      <c r="B265">
+        <v>975431844</v>
+      </c>
       <c r="C265" t="s">
         <v>268</v>
       </c>
@@ -6119,7 +6125,7 @@
       </c>
       <c r="E265" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">+51 </v>
+        <v>+51 975431844</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
@@ -6154,7 +6160,7 @@
         <v>58</v>
       </c>
       <c r="E267" t="str">
-        <f t="shared" ref="E267:E272" si="7">CONCATENATE("+",D267," ",B267)</f>
+        <f t="shared" ref="E267:E273" si="7">CONCATENATE("+",D267," ",B267)</f>
         <v>+58 412-8286364</v>
       </c>
     </row>
@@ -6198,15 +6204,18 @@
       <c r="A270" t="s">
         <v>427</v>
       </c>
-      <c r="B270" t="s">
-        <v>430</v>
+      <c r="B270">
+        <v>545039929</v>
       </c>
       <c r="C270" t="s">
         <v>429</v>
       </c>
+      <c r="D270">
+        <v>966</v>
+      </c>
       <c r="E270" t="str">
         <f t="shared" si="7"/>
-        <v>+ 966 545039929</v>
+        <v>+966 545039929</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
@@ -6228,9 +6237,39 @@
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>431</v>
+      </c>
+      <c r="B272">
+        <v>929423643</v>
+      </c>
+      <c r="C272" t="s">
+        <v>268</v>
+      </c>
+      <c r="D272">
+        <v>51</v>
+      </c>
       <c r="E272" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">+ </v>
+        <v>+51 929423643</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>430</v>
+      </c>
+      <c r="B273">
+        <v>992759838</v>
+      </c>
+      <c r="C273" t="s">
+        <v>312</v>
+      </c>
+      <c r="D273">
+        <v>593</v>
+      </c>
+      <c r="E273" t="str">
+        <f t="shared" si="7"/>
+        <v>+593 992759838</v>
       </c>
     </row>
   </sheetData>

--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15402F95-9C1F-43DB-954D-54833D934247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAFE7A31-2E87-48EC-8725-9849C26480B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="434">
   <si>
     <t>Darmanethan</t>
   </si>
@@ -1333,6 +1333,12 @@
   </si>
   <si>
     <t>DarkM17</t>
+  </si>
+  <si>
+    <t>LobilloS</t>
+  </si>
+  <si>
+    <t>1 672 103 1075</t>
   </si>
 </sst>
 </file>
@@ -1708,7 +1714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
-  <dimension ref="A1:E273"/>
+  <dimension ref="A1:E274"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
@@ -6272,6 +6278,24 @@
         <v>+593 992759838</v>
       </c>
     </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>432</v>
+      </c>
+      <c r="B274" t="s">
+        <v>433</v>
+      </c>
+      <c r="C274" t="s">
+        <v>265</v>
+      </c>
+      <c r="D274">
+        <v>52</v>
+      </c>
+      <c r="E274" t="str">
+        <f t="shared" ref="E274" si="8">CONCATENATE("+",D274," ",B274)</f>
+        <v>+52 1 672 103 1075</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E269" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A262">

--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAFE7A31-2E87-48EC-8725-9849C26480B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F6C3A8-28F8-4ED8-AD74-707850A718FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="435">
   <si>
     <t>Darmanethan</t>
   </si>
@@ -1339,6 +1339,9 @@
   </si>
   <si>
     <t>1 672 103 1075</t>
+  </si>
+  <si>
+    <t>Pain2007</t>
   </si>
 </sst>
 </file>
@@ -1714,7 +1717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
-  <dimension ref="A1:E274"/>
+  <dimension ref="A1:E275"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
@@ -6292,8 +6295,26 @@
         <v>52</v>
       </c>
       <c r="E274" t="str">
-        <f t="shared" ref="E274" si="8">CONCATENATE("+",D274," ",B274)</f>
+        <f t="shared" ref="E274:E275" si="8">CONCATENATE("+",D274," ",B274)</f>
         <v>+52 1 672 103 1075</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>434</v>
+      </c>
+      <c r="B275">
+        <v>963767681</v>
+      </c>
+      <c r="C275" t="s">
+        <v>312</v>
+      </c>
+      <c r="D275">
+        <v>593</v>
+      </c>
+      <c r="E275" t="str">
+        <f t="shared" si="8"/>
+        <v>+593 963767681</v>
       </c>
     </row>
   </sheetData>
